--- a/hrm/.plans/gop-db/finance-borrow-extend-request/testcase - Phieu yeu cau gia han hang muon.xlsx
+++ b/hrm/.plans/gop-db/finance-borrow-extend-request/testcase - Phieu yeu cau gia han hang muon.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q197"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.9" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,7 @@
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="5" t="n"/>
     </row>
-    <row r="3" ht="134" customHeight="1">
+    <row r="3" ht="151" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2. Đối tượng được tính / hiển thị</t>
@@ -631,8 +631,9 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Danh sách (lối vào thường) hiển thị phiếu theo phạm vi quyền, LUÔN bó trong công ty của người đăng nhập:
-- Có quyền "Xem phiếu hàng mượn theo tổng công ty" hoặc "Xem phiếu hàng mượn theo công ty": mọi phiếu của công ty mình.
+          <t>Danh sách (lối vào thường) hiển thị phiếu theo phạm vi quyền:
+- Super Admin hoặc có quyền "Xem phiếu hàng mượn theo tổng công ty": phiếu của MỌI công ty (muốn xem riêng một công ty thì chọn ở ô lọc Công ty).
+- Có quyền "Xem phiếu hàng mượn theo công ty": mọi phiếu của công ty mình.
 - Có quyền "Xem phiếu hàng mượn theo phòng ban": phiếu thuộc phòng ban mình quản lý, phòng ban của chính mình, và phiếu mình lập.
 - Không có quyền xem nào: chỉ phiếu mình lập.
 - Ngoài ra ai cũng thấy lại những phiếu mình ĐÃ duyệt hoặc đã từ chối (ở bất kỳ cấp nào).
@@ -661,10 +662,10 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>- Phiếu của công ty khác: không hiện trong danh sách, kể cả với quyền xem theo tổng công ty.
+          <t>- Phiếu của công ty khác: không hiện trong danh sách, TRỪ với Super Admin và người có quyền xem theo tổng công ty. Lối vào "chờ duyệt" thì luôn chỉ có phiếu cùng công ty.
 - Phiếu mượn của người khác, phiếu đã trả hết hàng, phiếu đang có yêu cầu gia hạn chờ duyệt: không hiện ở popup chọn phiếu.
 - Phiếu mượn có hạn trả hiện tại đã bằng hoặc sau ngày trần (hôm nay + số ngày mượn tối đa theo cấu hình): không hiện ở popup chọn phiếu.
-- Mặt hàng trên phiếu mượn không thuộc diện phải xuất: không hiện ở bảng Chi tiết hàng mượn, và bộ lọc Tên hàng hóa / Model cũng không dò trên các dòng này.
+- Mặt hàng trên phiếu mượn không thuộc diện phải xuất: không hiện ở bảng Chi tiết, và bộ lọc Tên hàng hóa / Model cũng không dò trên các dòng này.
 - Thao tác duyệt / từ chối làm bên cổng ERP cũ: không có trong Lịch sử thay đổi.</t>
         </is>
       </c>
@@ -715,7 +716,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Một phiếu gia hạn gắn với ĐÚNG MỘT phiếu yêu cầu xuất hàng mượn. Phiếu gia hạn KHÔNG có dòng hàng nhập tay: bảng "Chi tiết hàng mượn" đọc thẳng từ phiếu mượn và chỉ để xem.
+          <t>Một phiếu gia hạn gắn với ĐÚNG MỘT phiếu yêu cầu xuất hàng mượn. Phiếu gia hạn KHÔNG có dòng hàng nhập tay: bảng "Chi tiết" đọc thẳng từ phiếu mượn và chỉ để xem.
 Thông tin chính: Ngày hẹn trả (chụp lại từ phiếu mượn lúc lập), Ngày hẹn trả mới (1 ô cho cả phiếu), Ghi chú, File đính kèm (PDF).
 Phiếu có ba bộ thông tin duyệt cho ba cấp Trưởng phòng, Ban giám đốc, Kế toán; mỗi bộ gồm người thực hiện, thời điểm, ghi chú / lý do từ chối.
 Công ty và phòng ban của phiếu chốt theo người lập TẠI THỜI ĐIỂM LẬP.</t>
@@ -802,7 +803,7 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Thanh phân trang ghi tổng số phiếu khớp bộ lọc TRONG PHẠM VI QUYỀN của người đang xem.
-Bảng Chi tiết hàng mượn: "SL mượn" và "Đã trả" quy về đơn vị tính trên phiếu mượn; dòng "Tổng cộng" = tổng hai cột này.
+Bảng Chi tiết: "SL mượn" và "Đã trả" quy về đơn vị tính trên phiếu mượn; dòng "Tổng cộng" = tổng hai cột này.
 Hạn mức vượt cấp: tổng giá trị hàng còn nợ của phiếu mượn = cộng trên mọi dòng hàng (số lượng đã xuất trừ số lượng đã trả) nhân đơn giá. Tổng này LỚN HƠN hạn mức giá trị hàng mượn của công ty thì phiếu phải qua Ban giám đốc; bằng hoặc nhỏ hơn thì sang thẳng Kế toán.
 Ngày trần của Ngày hẹn trả mới = hôm nay + số ngày mượn tối đa theo cấu hình (tính từ HÔM NAY, không tính từ ngày hẹn trả cũ).
 Cột "Người duyệt / Ngày duyệt" ở danh sách = cấp đóng dấu SAU CÙNG (Kế toán, không có thì Ban giám đốc, không có nữa thì Trưởng phòng).</t>
@@ -821,7 +822,7 @@
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="5" t="n"/>
     </row>
-    <row r="10" ht="236" customHeight="1">
+    <row r="10" ht="253" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>9. Ghi chú đọc bảng</t>
@@ -831,8 +832,9 @@
         <is>
           <t>Các bẫy dễ bị ghi Failed oan:
 - Màn KHÔNG có nháp, KHÔNG có nút Sửa, KHÔNG có nút Xóa: đó là đúng thiết kế, không phải thiếu.
-- Quyền "Xem theo tổng công ty" ở danh sách vẫn chỉ thấy phiếu CÔNG TY MÌNH (giữ đúng như ERP), số phiếu bằng quyền "Xem theo công ty".
-- Hạn mức vượt cấp tính theo công ty của người duyệt (cũng chính là công ty ghi trên phiếu, vì chỉ duyệt được phiếu cùng công ty), không theo công ty người lập hiện tại.
+- Quyền "Xem theo tổng công ty" (và Super Admin) thấy phiếu của MỌI công ty ở lối vào thường (khác ERP — ERP bó về công ty mình); nhưng chỉ duyệt được phiếu cùng công ty.
+- Hạn mức vượt cấp lấy theo công ty GHI TRÊN PHIẾU (cũng là công ty người duyệt, vì chỉ duyệt được phiếu cùng công ty). Hạn mức của công ty để trống thì coi như 0: mọi phiếu mượn còn nợ đều phải qua Ban giám đốc.
+- Trưởng phòng nhận thông báo phiếu mới = đúng những Trưởng phòng duyệt được phiếu: quản lý phòng ban của phiếu, tích "Quản lý tất cả phòng ban", hoặc thuộc chính phòng ban của phiếu.
 - Chỉ Kế toán sửa được Ngày hẹn trả mới, và chỉ khi phiếu đang Chờ KT duyệt. Trưởng phòng và Ban giám đốc thấy ô này bị khoá là đúng.
 - Trưởng phòng duyệt xong mà phiếu chưa Đã duyệt là đúng: ngày hẹn trả của phiếu mượn chỉ đổi khi Kế toán duyệt.
 - Không phải phiếu nào cũng qua Ban giám đốc; dưới hạn mức thì nhảy thẳng sang Chờ KT duyệt.
@@ -1165,7 +1167,7 @@
       <c r="P19" s="16" t="inlineStr"/>
       <c r="Q19" s="16" t="inlineStr"/>
     </row>
-    <row r="20" ht="64" customHeight="1">
+    <row r="20" ht="89" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -1183,7 +1185,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Quyền "Xem phiếu hàng mượn theo tổng công ty" chỉ thấy phiếu công ty mình</t>
+          <t>Quyền "Xem phiếu hàng mượn theo tổng công ty" thấy phiếu mọi công ty</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -1202,19 +1204,20 @@
           <t>1. Đăng nhập bằng B.
 2. Vào phân hệ Tài chính &gt; nhóm "Hàng hoá - Dịch vụ - Vận chuyển" &gt; "Mượn hàng" &gt; bấm "Phiếu yêu cầu gia hạn hàng mượn".
 3. Đọc tổng số phiếu.
-4. Mở bộ lọc, xem ô Công ty.</t>
+4. Mở bộ lọc, chọn Công ty = công ty 4.</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Công ty: công ty 4</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>- Tổng số = N1, KHÔNG có phiếu nào của công ty 4.
+          <t>- Bước 3: tổng số = N1 + N4 (có cả phiếu của công ty 4, kể cả phiếu Chờ TP duyệt).
 - Bộ lọc có ô Công ty và ô Phòng ban.
-- Lưu ý: đây là hành vi giữ nguyên như ERP, không phải lỗi thiếu dữ liệu.</t>
+- Bước 4: còn đúng N4 phiếu.
+- Lưu ý: ERP bó về công ty mình; hệ thống mới cho thấy mọi công ty (khớp với việc mở được chi tiết phiếu công ty khác).</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr"/>
@@ -1238,7 +1241,7 @@
       <c r="P20" s="16" t="inlineStr"/>
       <c r="Q20" s="16" t="inlineStr"/>
     </row>
-    <row r="21" ht="58" customHeight="1">
+    <row r="21" ht="63" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -1283,7 +1286,7 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>- Tổng số = N1, bằng đúng con số của tài khoản B ở TC-ROLE-01.
+          <t>- Tổng số = N1 (ít hơn tài khoản B ở TC-ROLE-01 đúng N4 phiếu của công ty 4).
 - Có cả phiếu của các phòng ban khác trong công ty 1.
 - Có cả phiếu ở trạng thái Không duyệt do người khác lập.</t>
         </is>
@@ -3578,7 +3581,7 @@
       <c r="P55" s="16" t="inlineStr"/>
       <c r="Q55" s="16" t="inlineStr"/>
     </row>
-    <row r="56" ht="52" customHeight="1">
+    <row r="56" ht="49" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -3622,7 +3625,7 @@
       <c r="I56" s="15" t="inlineStr">
         <is>
           <t>- Ra phiếu gia hạn của PYCXH-35542 và các phiếu khác có mặt hàng tên chứa "Máy hàn".
-- Mở từng phiếu: bảng Chi tiết hàng mượn đều có mặt hàng chứa "Máy hàn".</t>
+- Mở từng phiếu: bảng Chi tiết đều có mặt hàng chứa "Máy hàn".</t>
         </is>
       </c>
       <c r="J56" s="15" t="inlineStr"/>
@@ -3646,7 +3649,7 @@
       <c r="P56" s="16" t="inlineStr"/>
       <c r="Q56" s="16" t="inlineStr"/>
     </row>
-    <row r="57" ht="44" customHeight="1">
+    <row r="57" ht="41" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -3674,7 +3677,7 @@
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn M có một dòng hàng "Kìm cắt" thuộc diện không phải xuất (không hiện ở bảng Chi tiết hàng mượn). Có 1 phiếu gia hạn cho M.</t>
+          <t>Phiếu mượn M có một dòng hàng "Kìm cắt" thuộc diện không phải xuất (không hiện ở bảng Chi tiết). Có 1 phiếu gia hạn cho M.</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
@@ -5133,7 +5136,7 @@
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="5" t="n"/>
     </row>
-    <row r="80" ht="144" customHeight="1">
+    <row r="80" ht="197" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -5177,8 +5180,9 @@
       <c r="I80" s="15" t="inlineStr">
         <is>
           <t>- Tiêu đề "Thêm yêu cầu gia hạn hàng mượn".
-- Khối "Thông tin chung": Phiếu yêu cầu xuất hàng mượn (bắt buộc, có nút "Chọn phiếu"), Ngày hẹn trả (khoá), Ngày hẹn trả mới (bắt buộc), Ngày tạo (khoá, là ngày hôm nay), Ghi chú.
-- Khối "File đính kèm" và khối "Chi tiết hàng mượn" (đang ghi "Chưa chọn phiếu mượn. Bấm Chọn phiếu ở trên để lấy danh sách hàng.").
+- Khối "Thông tin chung", góc phải ghi "&lt;tên người đăng nhập&gt; — &lt;ngày hôm nay&gt;"; các ô: Phiếu yêu cầu xuất hàng mượn (bắt buộc, có nút "Chọn phiếu"), Ngày hẹn trả (khoá), Ngày hẹn trả mới (bắt buộc), Ngày tạo (khoá, là ngày hôm nay), Ghi chú (gợi ý "Lý do cần gia hạn (không bắt buộc)").
+- Khối "File đính kèm" có nút "Thêm tài liệu" và các cột STT, UPLOAD / FILE, DUNG LƯỢNG.
+- Khối "Chi tiết" đang ghi "Chưa chọn phiếu mượn. Bấm Chọn phiếu ở trên để lấy danh sách hàng.".
 - Cuối màn có nút "Gửi duyệt" và "Lưu và tiếp tục"; KHÔNG có nút Lưu nháp.</t>
         </is>
       </c>
@@ -5754,7 +5758,7 @@
       <c r="P88" s="16" t="inlineStr"/>
       <c r="Q88" s="16" t="inlineStr"/>
     </row>
-    <row r="89" ht="95" customHeight="1">
+    <row r="89" ht="92" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -5799,7 +5803,7 @@
         <is>
           <t>- Popup đóng.
 - Ô Phiếu yêu cầu xuất hàng mượn = PYCXH-35542; Ngày hẹn trả = 23/09/2026.
-- Bảng Chi tiết hàng mượn có 3 dòng, cột: STT, Tên hàng hóa, Model, Mã hàng hóa, Thương hiệu, SL mượn, Đã trả, ĐVT; dòng "Tổng cộng" ở cuối.
+- Bảng Chi tiết có 3 dòng, cột: STT, Tên hàng hóa, Model, Mã hàng hóa, Thương hiệu, SL mượn, Đã trả, ĐVT; dòng "Tổng cộng" ở cuối.
 - Không phải nhập số lượng ở dòng nào (bảng chỉ để xem).</t>
         </is>
       </c>
@@ -5867,7 +5871,7 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>- Ô phiếu, Ngày hẹn trả và bảng Chi tiết hàng mượn đổi theo phiếu mới; không còn dòng của phiếu cũ.</t>
+          <t>- Ô phiếu, Ngày hẹn trả và bảng Chi tiết đổi theo phiếu mới; không còn dòng của phiếu cũ.</t>
         </is>
       </c>
       <c r="J90" s="15" t="inlineStr"/>
@@ -6245,7 +6249,7 @@
       <c r="P95" s="16" t="inlineStr"/>
       <c r="Q95" s="16" t="inlineStr"/>
     </row>
-    <row r="96" ht="48" customHeight="1">
+    <row r="96" ht="51" customHeight="1">
       <c r="A96" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -6273,7 +6277,7 @@
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>Trưởng phòng E có quyền Trưởng phòng duyệt hàng mượn và quản lý phòng P1; Trưởng phòng E2 có quyền nhưng quản lý phòng P2.</t>
+          <t>Trưởng phòng E có quyền Trưởng phòng duyệt hàng mượn và quản lý phòng P1; Trưởng phòng E2 có quyền nhưng chỉ quản lý phòng P2, bản thân E2 cũng thuộc P2.</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -6590,30 +6594,78 @@
       <c r="P100" s="16" t="inlineStr"/>
       <c r="Q100" s="16" t="inlineStr"/>
     </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="A101" s="13" t="n"/>
-      <c r="B101" s="13" t="n"/>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>V. XEM CHI TIẾT</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
-      <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="n"/>
-      <c r="J101" s="4" t="n"/>
-      <c r="K101" s="4" t="n"/>
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="4" t="n"/>
-      <c r="N101" s="4" t="n"/>
-      <c r="O101" s="4" t="n"/>
-      <c r="P101" s="4" t="n"/>
-      <c r="Q101" s="5" t="n"/>
-    </row>
-    <row r="102" ht="128" customHeight="1">
+    <row r="101" ht="85" customHeight="1">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>LẬP PHIẾU (TẠO MỚI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>TC_04.022</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>Trưởng phòng thuộc chính phòng ban của phiếu nhận thông báo và duyệt được</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>Trưởng phòng E5 có quyền Trưởng phòng duyệt hàng mượn, bản thân thuộc phòng P1 nhưng KHÔNG được phân công quản lý phòng nào.</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>1. Nhân viên phòng P1 gửi một phiếu.
+2. Kiểm tra chuông thông báo của E5.
+3. E5 bấm vào thông báo.</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>- E5 nhận thông báo "[PGHHM] Chờ duyệt: &lt;mã phiếu&gt;."
+- Mở đúng màn chi tiết, có nút "TP duyệt" và "Từ chối".
+- Lưu ý: trước đây người duyệt được nhưng không nhận thông báo (Redmine #11550), nay "duyệt được" và "nhận được thông báo" là cùng một nhóm người.</t>
+        </is>
+      </c>
+      <c r="J101" s="15" t="inlineStr"/>
+      <c r="K101" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L101" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N101" s="15" t="inlineStr"/>
+      <c r="O101" s="16" t="inlineStr"/>
+      <c r="P101" s="16" t="inlineStr"/>
+      <c r="Q101" s="16" t="inlineStr"/>
+    </row>
+    <row r="102" ht="42" customHeight="1">
       <c r="A102" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -6621,32 +6673,34 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>XEM CHI TIẾT</t>
+          <t>LẬP PHIẾU (TẠO MỚI)</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
         <is>
-          <t>TC_05.001</t>
+          <t>TC_04.023</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Bố cục màn chi tiết</t>
+          <t>Trưởng phòng tích "Quản lý tất cả phòng ban" nhận thông báo và duyệt được</t>
         </is>
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>Phiếu PGHHM-02930 ở trạng thái Chờ TP duyệt, có 2 file đính kèm.</t>
+          <t>Trưởng phòng E6 có quyền Trưởng phòng duyệt hàng mượn, được tích "Quản lý tất cả phòng ban" ở công ty 1, không thuộc phòng P1.</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết PGHHM-02930.</t>
+          <t>1. Nhân viên phòng P1 (công ty 1) gửi một phiếu.
+2. Kiểm tra chuông thông báo của E6.
+3. E6 mở phiếu.</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
@@ -6656,10 +6710,8 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>- Tiêu đề "Chi tiết yêu cầu gia hạn hàng mượn: PGHHM-02930".
-- Khối Thông tin chung có nhãn trạng thái ở góc phải; ô Mã phiếu, Phiếu yêu cầu xuất hàng mượn, Người tạo, Phòng ban yêu cầu, Ngày hẹn trả, Ngày hẹn trả mới, Ngày tạo, Ghi chú.
-- Khối File đính kèm (chỉ xem), Chi tiết hàng mượn, Lịch sử thay đổi (thu gọn sẵn).
-- Mọi ô thông tin đều khoá (trừ trường hợp Kế toán ở TC_05.004).</t>
+          <t>- E6 nhận thông báo "[PGHHM] Chờ duyệt: &lt;mã phiếu&gt;."
+- Phiếu có nút "TP duyệt" và "Từ chối" với E6.</t>
         </is>
       </c>
       <c r="J102" s="15" t="inlineStr"/>
@@ -6683,7 +6735,7 @@
       <c r="P102" s="16" t="inlineStr"/>
       <c r="Q102" s="16" t="inlineStr"/>
     </row>
-    <row r="103" ht="34" customHeight="1">
+    <row r="103" ht="52" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -6691,17 +6743,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>XEM CHI TIẾT</t>
+          <t>LẬP PHIẾU (TẠO MỚI)</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>TC_05.002</t>
+          <t>TC_04.024</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>Đang tải không hiện như phiếu rỗng</t>
+          <t>Sắp xếp trong popup chọn phiếu mượn</t>
         </is>
       </c>
       <c r="E103" s="16" t="inlineStr">
@@ -6711,12 +6763,13 @@
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>Mạng chậm.</t>
+          <t>A có ít nhất 3 phiếu mượn đủ điều kiện, ngày tạo và ngày hẹn trả khác nhau.</t>
         </is>
       </c>
       <c r="G103" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết một phiếu.</t>
+          <t>1. Mở popup chọn phiếu.
+2. Bấm lần lượt tiêu đề Mã phiếu, Ngày tạo, Ngày hẹn trả; mỗi cột bấm 2 lần.</t>
         </is>
       </c>
       <c r="H103" s="15" t="inlineStr">
@@ -6726,8 +6779,9 @@
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
-          <t>- Trong lúc chờ hiện "Đang tải dữ liệu phiếu...".
-- KHÔNG nhấp nháy dòng "Chưa chọn phiếu mượn".</t>
+          <t>- Mặc định phiếu tạo mới nhất ở đầu.
+- Ba cột Mã phiếu, Ngày tạo, Ngày hẹn trả đổi được tăng / giảm dần, dữ liệu xếp đúng.
+- Cột Ghi chú không sắp xếp được.</t>
         </is>
       </c>
       <c r="J103" s="15" t="inlineStr"/>
@@ -6751,121 +6805,76 @@
       <c r="P103" s="16" t="inlineStr"/>
       <c r="Q103" s="16" t="inlineStr"/>
     </row>
-    <row r="104" ht="34" customHeight="1">
-      <c r="A104" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="13" t="n"/>
+      <c r="B104" s="13" t="n"/>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>V. XEM CHI TIẾT</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
+      <c r="P104" s="4" t="n"/>
+      <c r="Q104" s="5" t="n"/>
+    </row>
+    <row r="105" ht="152" customHeight="1">
+      <c r="A105" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
         <is>
           <t>XEM CHI TIẾT</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>TC_05.003</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>Liên kết phiếu mượn mở tab mới</t>
-        </is>
-      </c>
-      <c r="E104" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F104" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu gắn với PYCXH-35542.</t>
-        </is>
-      </c>
-      <c r="G104" s="15" t="inlineStr">
-        <is>
-          <t>1. Bấm vào PYCXH-35542 ở ô Phiếu yêu cầu xuất hàng mượn.</t>
-        </is>
-      </c>
-      <c r="H104" s="15" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>TC_05.001</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>Bố cục màn chi tiết</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu PGHHM-02930 ở trạng thái Chờ TP duyệt, có 2 file đính kèm.</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở chi tiết PGHHM-02930.</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t>- Mở TAB MỚI màn chi tiết phiếu yêu cầu xuất hàng PYCXH-35542.</t>
-        </is>
-      </c>
-      <c r="J104" s="15" t="inlineStr"/>
-      <c r="K104" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L104" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M104" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N104" s="15" t="inlineStr"/>
-      <c r="O104" s="16" t="inlineStr"/>
-      <c r="P104" s="16" t="inlineStr"/>
-      <c r="Q104" s="16" t="inlineStr"/>
-    </row>
-    <row r="105" ht="55" customHeight="1">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t>XEM CHI TIẾT</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>TC_05.004</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>Ô Ngày hẹn trả mới khoá / mở theo người xem</t>
-        </is>
-      </c>
-      <c r="E105" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu X Chờ TP duyệt; phiếu Y Chờ KT duyệt.</t>
-        </is>
-      </c>
-      <c r="G105" s="15" t="inlineStr">
-        <is>
-          <t>1. Trưởng phòng E mở X.
-2. Kế toán G mở Y.
-3. Người lập mở Y.</t>
-        </is>
-      </c>
-      <c r="H105" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I105" s="15" t="inlineStr">
         <is>
-          <t>- E: ô khoá, biểu tượng chữ i ghi "Chỉ Kế toán được sửa lại ngày này, và chỉ khi phiếu đang chờ Kế toán duyệt."
-- G: ô mở khoá, có dấu bắt buộc.
-- Người lập: ô khoá.</t>
+          <t>- Tiêu đề "Chi tiết yêu cầu gia hạn hàng mượn: PGHHM-02930".
+- Khối Thông tin chung, góc phải ghi "&lt;người tạo&gt; — &lt;ngày giờ tạo&gt;" (không còn nhãn trạng thái); các ô Mã phiếu, Phiếu yêu cầu xuất hàng mượn (liên kết), Người tạo, Phòng ban yêu cầu, Ngày hẹn trả, Ngày hẹn trả mới, Ngày tạo, Ghi chú.
+- Khối File đính kèm (xem / tải về, có cột Dung lượng), Chi tiết, Lịch sử thay đổi (thu gọn sẵn).
+- Mọi ô thông tin đều khoá (trừ trường hợp Kế toán ở TC_05.004).</t>
         </is>
       </c>
       <c r="J105" s="15" t="inlineStr"/>
@@ -6902,27 +6911,27 @@
       </c>
       <c r="C106" s="16" t="inlineStr">
         <is>
-          <t>TC_05.005</t>
+          <t>TC_05.002</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>Số lượng hiển thị theo chuẩn quốc tế</t>
+          <t>Đang tải không hiện như phiếu rỗng</t>
         </is>
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn có mặt hàng SL mượn 1,250 và đã trả 12.5.</t>
+          <t>Mạng chậm.</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết, xem bảng Chi tiết hàng mượn.</t>
+          <t>1. Mở chi tiết một phiếu.</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
@@ -6932,8 +6941,8 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>- SL mượn hiện "1,250"; Đã trả hiện "12.5" (không có số 0 thừa).
-- Dòng Tổng cộng cộng đúng hai cột.</t>
+          <t>- Trong lúc chờ hiện "Đang tải dữ liệu phiếu...".
+- KHÔNG nhấp nháy dòng "Chưa chọn phiếu mượn".</t>
         </is>
       </c>
       <c r="J106" s="15" t="inlineStr"/>
@@ -6957,7 +6966,7 @@
       <c r="P106" s="16" t="inlineStr"/>
       <c r="Q106" s="16" t="inlineStr"/>
     </row>
-    <row r="107" ht="69" customHeight="1">
+    <row r="107" ht="34" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -6970,27 +6979,27 @@
       </c>
       <c r="C107" s="16" t="inlineStr">
         <is>
-          <t>TC_05.006</t>
+          <t>TC_05.003</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Khối Lịch sử duyệt liệt kê đủ các cấp đã đóng dấu</t>
+          <t>Liên kết phiếu mượn mở tab mới</t>
         </is>
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>Phiếu đã qua Trưởng phòng E, Ban giám đốc F, Kế toán G (Đã duyệt).</t>
+          <t>Phiếu gắn với PYCXH-35542.</t>
         </is>
       </c>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết phiếu.</t>
+          <t>1. Bấm vào PYCXH-35542 ở ô Phiếu yêu cầu xuất hàng mượn.</t>
         </is>
       </c>
       <c r="H107" s="15" t="inlineStr">
@@ -7000,9 +7009,7 @@
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
-          <t>- Khối "Lịch sử duyệt" có 3 dòng theo thứ tự Trưởng phòng, Ban giám đốc, Kế toán.
-- Cột: STT, Cấp duyệt, Người duyệt, Thời gian, Ghi chú.
-- Lưu ý: ERP bỏ sót cấp Ban giám đốc ở khối này; hệ thống mới hiện đủ.</t>
+          <t>- Mở TAB MỚI màn chi tiết phiếu yêu cầu xuất hàng PYCXH-35542.</t>
         </is>
       </c>
       <c r="J107" s="15" t="inlineStr"/>
@@ -7026,7 +7033,7 @@
       <c r="P107" s="16" t="inlineStr"/>
       <c r="Q107" s="16" t="inlineStr"/>
     </row>
-    <row r="108" ht="34" customHeight="1">
+    <row r="108" ht="55" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -7039,12 +7046,12 @@
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>TC_05.007</t>
+          <t>TC_05.004</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Khối Lịch sử duyệt đánh dấu cấp đã từ chối</t>
+          <t>Ô Ngày hẹn trả mới khoá / mở theo người xem</t>
         </is>
       </c>
       <c r="E108" s="16" t="inlineStr">
@@ -7054,12 +7061,14 @@
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>Phiếu bị Trưởng phòng E từ chối với lý do "Chưa trả hàng kỳ trước".</t>
+          <t>Phiếu X Chờ TP duyệt; phiếu Y Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết phiếu.</t>
+          <t>1. Trưởng phòng E mở X.
+2. Kế toán G mở Y.
+3. Người lập mở Y.</t>
         </is>
       </c>
       <c r="H108" s="15" t="inlineStr">
@@ -7069,7 +7078,9 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>- Có 1 dòng "Trưởng phòng" kèm nhãn đỏ "Từ chối", cột Ghi chú = "Chưa trả hàng kỳ trước".</t>
+          <t>- E: ô khoá, biểu tượng chữ i ghi "Chỉ Kế toán được sửa lại ngày này, và chỉ khi phiếu đang chờ Kế toán duyệt."
+- G: ô mở khoá, có dấu bắt buộc.
+- Người lập: ô khoá.</t>
         </is>
       </c>
       <c r="J108" s="15" t="inlineStr"/>
@@ -7106,27 +7117,27 @@
       </c>
       <c r="C109" s="16" t="inlineStr">
         <is>
-          <t>TC_05.008</t>
+          <t>TC_05.005</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>Phiếu chưa ai duyệt không có khối Lịch sử duyệt</t>
+          <t>Số lượng hiển thị theo chuẩn quốc tế</t>
         </is>
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>Phiếu vừa lập, Chờ TP duyệt.</t>
+          <t>Phiếu mượn có mặt hàng SL mượn 1,250 và đã trả 12.5.</t>
         </is>
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết phiếu.</t>
+          <t>1. Mở chi tiết, xem bảng Chi tiết.</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
@@ -7136,7 +7147,8 @@
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
-          <t>- Không hiện khối "Lịch sử duyệt".</t>
+          <t>- SL mượn hiện "1,250"; Đã trả hiện "12.5" (không có số 0 thừa).
+- Dòng Tổng cộng cộng đúng hai cột.</t>
         </is>
       </c>
       <c r="J109" s="15" t="inlineStr"/>
@@ -7160,7 +7172,7 @@
       <c r="P109" s="16" t="inlineStr"/>
       <c r="Q109" s="16" t="inlineStr"/>
     </row>
-    <row r="110" ht="34" customHeight="1">
+    <row r="110" ht="69" customHeight="1">
       <c r="A110" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -7173,12 +7185,12 @@
       </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>TC_05.009</t>
+          <t>TC_05.006</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Nút ở cuối màn theo trạng thái</t>
+          <t>Khối Lịch sử duyệt liệt kê đủ các cấp đã đóng dấu</t>
         </is>
       </c>
       <c r="E110" s="16" t="inlineStr">
@@ -7188,12 +7200,12 @@
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>Người lập A mở phiếu của mình ở từng trạng thái.</t>
+          <t>Phiếu đã qua Trưởng phòng E, Ban giám đốc F, Kế toán G (Đã duyệt).</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
         <is>
-          <t>1. Mở phiếu Chờ TP duyệt, Đã duyệt, Không duyệt.</t>
+          <t>1. Mở chi tiết phiếu.</t>
         </is>
       </c>
       <c r="H110" s="15" t="inlineStr">
@@ -7203,8 +7215,9 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>- Cả ba chỉ có nút "In" và nút quay lại.
-- KHÔNG có nút Sửa, Xóa, Gửi lại (bị ẩn hẳn, không phải mờ).</t>
+          <t>- Khối "Lịch sử duyệt" có 3 dòng theo thứ tự Trưởng phòng, Ban giám đốc, Kế toán.
+- Cột: STT, Cấp duyệt, Người duyệt, Thời gian, Ghi chú.
+- Lưu ý: ERP bỏ sót cấp Ban giám đốc ở khối này; hệ thống mới hiện đủ.</t>
         </is>
       </c>
       <c r="J110" s="15" t="inlineStr"/>
@@ -7241,27 +7254,27 @@
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>TC_05.010</t>
+          <t>TC_05.007</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>Người có quyền xem theo phòng ban mở phiếu phòng mình quản lý</t>
+          <t>Khối Lịch sử duyệt đánh dấu cấp đã từ chối</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>D có quyền Xem theo phòng ban, quản lý P1. Phiếu Z thuộc P1 do người khác lập.</t>
+          <t>Phiếu bị Trưởng phòng E từ chối với lý do "Chưa trả hàng kỳ trước".</t>
         </is>
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
-          <t>1. D mở chi tiết Z từ danh sách.</t>
+          <t>1. Mở chi tiết phiếu.</t>
         </is>
       </c>
       <c r="H111" s="15" t="inlineStr">
@@ -7271,7 +7284,7 @@
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
-          <t>- Xem được đầy đủ nội dung, không báo lỗi quyền.</t>
+          <t>- Có 1 dòng "Trưởng phòng" kèm nhãn đỏ "Từ chối", cột Ghi chú = "Chưa trả hàng kỳ trước".</t>
         </is>
       </c>
       <c r="J111" s="15" t="inlineStr"/>
@@ -7308,28 +7321,27 @@
       </c>
       <c r="C112" s="16" t="inlineStr">
         <is>
-          <t>TC_05.011</t>
+          <t>TC_05.008</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Người đã duyệt vẫn mở lại được phiếu</t>
+          <t>Phiếu chưa ai duyệt không có khối Lịch sử duyệt</t>
         </is>
       </c>
       <c r="E112" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>E chỉ có quyền Trưởng phòng duyệt, đã duyệt phiếu X (nay Chờ KT duyệt).</t>
+          <t>Phiếu vừa lập, Chờ TP duyệt.</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>1. E tìm X ở danh sách lối vào thường.
-2. Mở chi tiết X.</t>
+          <t>1. Mở chi tiết phiếu.</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
@@ -7339,8 +7351,7 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>- X có trong danh sách của E.
-- Mở xem được, không có nút duyệt (đã qua cấp của E).</t>
+          <t>- Không hiện khối "Lịch sử duyệt".</t>
         </is>
       </c>
       <c r="J112" s="15" t="inlineStr"/>
@@ -7364,73 +7375,277 @@
       <c r="P112" s="16" t="inlineStr"/>
       <c r="Q112" s="16" t="inlineStr"/>
     </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="13" t="n"/>
-      <c r="B113" s="13" t="n"/>
-      <c r="C113" s="14" t="inlineStr">
+    <row r="113" ht="34" customHeight="1">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>XEM CHI TIẾT</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>TC_05.009</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Nút ở cuối màn theo trạng thái</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>Người lập A mở phiếu của mình ở từng trạng thái.</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở phiếu Chờ TP duyệt, Đã duyệt, Không duyệt.</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>- Cả ba chỉ có nút "In" và nút quay lại.
+- KHÔNG có nút Sửa, Xóa, Gửi lại (bị ẩn hẳn, không phải mờ).</t>
+        </is>
+      </c>
+      <c r="J113" s="15" t="inlineStr"/>
+      <c r="K113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N113" s="15" t="inlineStr"/>
+      <c r="O113" s="16" t="inlineStr"/>
+      <c r="P113" s="16" t="inlineStr"/>
+      <c r="Q113" s="16" t="inlineStr"/>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>XEM CHI TIẾT</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>TC_05.010</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>Người có quyền xem theo phòng ban mở phiếu phòng mình quản lý</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>D có quyền Xem theo phòng ban, quản lý P1. Phiếu Z thuộc P1 do người khác lập.</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="inlineStr">
+        <is>
+          <t>1. D mở chi tiết Z từ danh sách.</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>- Xem được đầy đủ nội dung, không báo lỗi quyền.</t>
+        </is>
+      </c>
+      <c r="J114" s="15" t="inlineStr"/>
+      <c r="K114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N114" s="15" t="inlineStr"/>
+      <c r="O114" s="16" t="inlineStr"/>
+      <c r="P114" s="16" t="inlineStr"/>
+      <c r="Q114" s="16" t="inlineStr"/>
+    </row>
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>XEM CHI TIẾT</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>TC_05.011</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>Người đã duyệt vẫn mở lại được phiếu</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>E chỉ có quyền Trưởng phòng duyệt, đã duyệt phiếu X (nay Chờ KT duyệt).</t>
+        </is>
+      </c>
+      <c r="G115" s="15" t="inlineStr">
+        <is>
+          <t>1. E tìm X ở danh sách lối vào thường.
+2. Mở chi tiết X.</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="15" t="inlineStr">
+        <is>
+          <t>- X có trong danh sách của E.
+- Mở xem được, không có nút duyệt (đã qua cấp của E).</t>
+        </is>
+      </c>
+      <c r="J115" s="15" t="inlineStr"/>
+      <c r="K115" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L115" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N115" s="15" t="inlineStr"/>
+      <c r="O115" s="16" t="inlineStr"/>
+      <c r="P115" s="16" t="inlineStr"/>
+      <c r="Q115" s="16" t="inlineStr"/>
+    </row>
+    <row r="116" ht="26" customHeight="1">
+      <c r="A116" s="13" t="n"/>
+      <c r="B116" s="13" t="n"/>
+      <c r="C116" s="14" t="inlineStr">
         <is>
           <t>VI. DUYỆT &amp; TỪ CHỐI</t>
         </is>
       </c>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="n"/>
-      <c r="L113" s="4" t="n"/>
-      <c r="M113" s="4" t="n"/>
-      <c r="N113" s="4" t="n"/>
-      <c r="O113" s="4" t="n"/>
-      <c r="P113" s="4" t="n"/>
-      <c r="Q113" s="5" t="n"/>
-    </row>
-    <row r="114" ht="76" customHeight="1">
-      <c r="A114" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B114" s="15" t="inlineStr">
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="n"/>
+      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="4" t="n"/>
+      <c r="L116" s="4" t="n"/>
+      <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="n"/>
+      <c r="P116" s="4" t="n"/>
+      <c r="Q116" s="5" t="n"/>
+    </row>
+    <row r="117" ht="76" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
         <is>
           <t>DUYỆT &amp; TỪ CHỐI</t>
         </is>
       </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="C117" s="16" t="inlineStr">
         <is>
           <t>TC_06.001</t>
         </is>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>Trưởng phòng duyệt phiếu dưới hạn mức sang thẳng Kế toán</t>
         </is>
       </c>
-      <c r="E114" s="16" t="inlineStr">
+      <c r="E117" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F114" s="15" t="inlineStr">
+      <c r="F117" s="15" t="inlineStr">
         <is>
           <t>Hạn mức giá trị hàng mượn công ty 1 = 20,000,000.
 Phiếu X (phòng P1) gắn phiếu mượn còn nợ 5,000,000. E quản lý P1.</t>
         </is>
       </c>
-      <c r="G114" s="15" t="inlineStr">
+      <c r="G117" s="15" t="inlineStr">
         <is>
           <t>1. E mở X, bấm "TP duyệt".
 2. Đọc popup xác nhận, bấm "Duyệt".</t>
         </is>
       </c>
-      <c r="H114" s="15" t="inlineStr">
+      <c r="H117" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I114" s="15" t="inlineStr">
+      <c r="I117" s="15" t="inlineStr">
         <is>
           <t>- Popup "Xác nhận duyệt" ghi "Bạn xác nhận TP duyệt phiếu &lt;mã&gt;?", nút "Duyệt" màu xanh.
 - Thông báo "Yêu cầu đã được chuyển đến Kế toán."
@@ -7438,209 +7653,6 @@
 - Ngày hẹn trả của phiếu mượn KHÔNG đổi.</t>
         </is>
       </c>
-      <c r="J114" s="15" t="inlineStr"/>
-      <c r="K114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M114" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N114" s="15" t="inlineStr"/>
-      <c r="O114" s="16" t="inlineStr"/>
-      <c r="P114" s="16" t="inlineStr"/>
-      <c r="Q114" s="16" t="inlineStr"/>
-    </row>
-    <row r="115" ht="34" customHeight="1">
-      <c r="A115" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B115" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.002</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>Trưởng phòng duyệt phiếu vượt hạn mức lên Ban giám đốc</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="inlineStr">
-        <is>
-          <t>Hạn mức công ty 1 = 20,000,000. Phiếu Y gắn phiếu mượn còn nợ 25,000,000.</t>
-        </is>
-      </c>
-      <c r="G115" s="15" t="inlineStr">
-        <is>
-          <t>1. E mở Y, bấm "TP duyệt", xác nhận.</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>- Thông báo "Yêu cầu đã được chuyển đến Ban giám đốc."
-- Y ở trạng thái Chờ BGĐ duyệt.</t>
-        </is>
-      </c>
-      <c r="J115" s="15" t="inlineStr"/>
-      <c r="K115" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L115" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M115" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N115" s="15" t="inlineStr"/>
-      <c r="O115" s="16" t="inlineStr"/>
-      <c r="P115" s="16" t="inlineStr"/>
-      <c r="Q115" s="16" t="inlineStr"/>
-    </row>
-    <row r="116" ht="34" customHeight="1">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.003</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>Giá trị còn nợ bằng đúng hạn mức không phải qua Ban giám đốc</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F116" s="15" t="inlineStr">
-        <is>
-          <t>Hạn mức 20,000,000. Phiếu gắn phiếu mượn còn nợ đúng 20,000,000.</t>
-        </is>
-      </c>
-      <c r="G116" s="15" t="inlineStr">
-        <is>
-          <t>1. Trưởng phòng duyệt phiếu.</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I116" s="15" t="inlineStr">
-        <is>
-          <t>- Phiếu sang Chờ KT duyệt (chỉ LỚN HƠN hạn mức mới lên Ban giám đốc).</t>
-        </is>
-      </c>
-      <c r="J116" s="15" t="inlineStr"/>
-      <c r="K116" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L116" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M116" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N116" s="15" t="inlineStr"/>
-      <c r="O116" s="16" t="inlineStr"/>
-      <c r="P116" s="16" t="inlineStr"/>
-      <c r="Q116" s="16" t="inlineStr"/>
-    </row>
-    <row r="117" ht="48" customHeight="1">
-      <c r="A117" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B117" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.004</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>Giá trị còn nợ chỉ tính phần chưa trả</t>
-        </is>
-      </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F117" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu mượn có 1 dòng: xuất 10 cái, đã trả 6 cái, đơn giá 6,000,000 (còn nợ 24,000,000). Hạn mức 20,000,000.</t>
-        </is>
-      </c>
-      <c r="G117" s="15" t="inlineStr">
-        <is>
-          <t>1. Trưởng phòng duyệt phiếu gia hạn của phiếu mượn này.</t>
-        </is>
-      </c>
-      <c r="H117" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="15" t="inlineStr">
-        <is>
-          <t>- Phiếu sang Chờ BGĐ duyệt (24,000,000 lớn hơn 20,000,000).
-- Nếu trả thêm 1 cái trước khi duyệt (còn nợ 18,000,000) thì sang thẳng Chờ KT duyệt.</t>
-        </is>
-      </c>
       <c r="J117" s="15" t="inlineStr"/>
       <c r="K117" s="16" t="inlineStr">
         <is>
@@ -7662,7 +7674,7 @@
       <c r="P117" s="16" t="inlineStr"/>
       <c r="Q117" s="16" t="inlineStr"/>
     </row>
-    <row r="118" ht="57" customHeight="1">
+    <row r="118" ht="34" customHeight="1">
       <c r="A118" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -7675,12 +7687,12 @@
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>TC_06.005</t>
+          <t>TC_06.002</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Ban giám đốc duyệt</t>
+          <t>Trưởng phòng duyệt phiếu vượt hạn mức lên Ban giám đốc</t>
         </is>
       </c>
       <c r="E118" s="16" t="inlineStr">
@@ -7690,12 +7702,12 @@
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>Phiếu Y Chờ BGĐ duyệt; F có quyền Ban giám đốc duyệt hàng mượn, cùng công ty.</t>
+          <t>Hạn mức công ty 1 = 20,000,000. Phiếu Y gắn phiếu mượn còn nợ 25,000,000.</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>1. F mở Y, bấm "BGĐ duyệt", xác nhận.</t>
+          <t>1. E mở Y, bấm "TP duyệt", xác nhận.</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
@@ -7705,9 +7717,8 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>- Thông báo "Yêu cầu đã được chuyển đến Kế toán."
-- Quay về danh sách; Y ở Chờ KT duyệt.
-- Người có quyền Kế toán kho cùng công ty nhận thông báo "[PGHHM] Chờ duyệt: &lt;mã&gt;."</t>
+          <t>- Thông báo "Yêu cầu đã được chuyển đến Ban giám đốc."
+- Y ở trạng thái Chờ BGĐ duyệt.</t>
         </is>
       </c>
       <c r="J118" s="15" t="inlineStr"/>
@@ -7731,7 +7742,7 @@
       <c r="P118" s="16" t="inlineStr"/>
       <c r="Q118" s="16" t="inlineStr"/>
     </row>
-    <row r="119" ht="110" customHeight="1">
+    <row r="119" ht="34" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -7744,37 +7755,241 @@
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
+          <t>TC_06.003</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>Giá trị còn nợ bằng đúng hạn mức không phải qua Ban giám đốc</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F119" s="15" t="inlineStr">
+        <is>
+          <t>Hạn mức 20,000,000. Phiếu gắn phiếu mượn còn nợ đúng 20,000,000.</t>
+        </is>
+      </c>
+      <c r="G119" s="15" t="inlineStr">
+        <is>
+          <t>1. Trưởng phòng duyệt phiếu.</t>
+        </is>
+      </c>
+      <c r="H119" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>- Phiếu sang Chờ KT duyệt (chỉ LỚN HƠN hạn mức mới lên Ban giám đốc).</t>
+        </is>
+      </c>
+      <c r="J119" s="15" t="inlineStr"/>
+      <c r="K119" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L119" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N119" s="15" t="inlineStr"/>
+      <c r="O119" s="16" t="inlineStr"/>
+      <c r="P119" s="16" t="inlineStr"/>
+      <c r="Q119" s="16" t="inlineStr"/>
+    </row>
+    <row r="120" ht="48" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>TC_06.004</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Giá trị còn nợ chỉ tính phần chưa trả</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F120" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu mượn có 1 dòng: xuất 10 cái, đã trả 6 cái, đơn giá 6,000,000 (còn nợ 24,000,000). Hạn mức 20,000,000.</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="inlineStr">
+        <is>
+          <t>1. Trưởng phòng duyệt phiếu gia hạn của phiếu mượn này.</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>- Phiếu sang Chờ BGĐ duyệt (24,000,000 lớn hơn 20,000,000).
+- Nếu trả thêm 1 cái trước khi duyệt (còn nợ 18,000,000) thì sang thẳng Chờ KT duyệt.</t>
+        </is>
+      </c>
+      <c r="J120" s="15" t="inlineStr"/>
+      <c r="K120" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L120" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N120" s="15" t="inlineStr"/>
+      <c r="O120" s="16" t="inlineStr"/>
+      <c r="P120" s="16" t="inlineStr"/>
+      <c r="Q120" s="16" t="inlineStr"/>
+    </row>
+    <row r="121" ht="57" customHeight="1">
+      <c r="A121" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>TC_06.005</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>Ban giám đốc duyệt</t>
+        </is>
+      </c>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu Y Chờ BGĐ duyệt; F có quyền Ban giám đốc duyệt hàng mượn, cùng công ty.</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="inlineStr">
+        <is>
+          <t>1. F mở Y, bấm "BGĐ duyệt", xác nhận.</t>
+        </is>
+      </c>
+      <c r="H121" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>- Thông báo "Yêu cầu đã được chuyển đến Kế toán."
+- Quay về danh sách; Y ở Chờ KT duyệt.
+- Người có quyền Kế toán kho cùng công ty nhận thông báo "[PGHHM] Chờ duyệt: &lt;mã&gt;."</t>
+        </is>
+      </c>
+      <c r="J121" s="15" t="inlineStr"/>
+      <c r="K121" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L121" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N121" s="15" t="inlineStr"/>
+      <c r="O121" s="16" t="inlineStr"/>
+      <c r="P121" s="16" t="inlineStr"/>
+      <c r="Q121" s="16" t="inlineStr"/>
+    </row>
+    <row r="122" ht="110" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
           <t>TC_06.006</t>
         </is>
       </c>
-      <c r="D119" s="15" t="inlineStr">
+      <c r="D122" s="15" t="inlineStr">
         <is>
           <t>Kế toán duyệt giữ nguyên ngày, phiếu mượn đổi hạn trả</t>
         </is>
       </c>
-      <c r="E119" s="16" t="inlineStr">
+      <c r="E122" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F119" s="15" t="inlineStr">
+      <c r="F122" s="15" t="inlineStr">
         <is>
           <t>Phiếu N Chờ KT duyệt, Ngày hẹn trả mới 05/10/2026, gắn phiếu mượn PYCXH-35542 hạn 23/09/2026.</t>
         </is>
       </c>
-      <c r="G119" s="15" t="inlineStr">
+      <c r="G122" s="15" t="inlineStr">
         <is>
           <t>1. G mở N, không sửa ngày, bấm "KT duyệt".
 2. Đọc popup, bấm "Duyệt".
 3. Mở phiếu PYCXH-35542.</t>
         </is>
       </c>
-      <c r="H119" s="15" t="inlineStr">
+      <c r="H122" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I119" s="15" t="inlineStr">
+      <c r="I122" s="15" t="inlineStr">
         <is>
           <t>- Popup ghi "Duyệt bước Kế toán sẽ đổi ngày hẹn trả của phiếu mượn PYCXH-35542 sang 05/10/2026 ngay lập tức. Bạn có chắc chắn không?"
 - Thông báo "Duyệt phiếu thành công."; quay về danh sách; N Đã duyệt.
@@ -7782,216 +7997,6 @@
 - Người lập nhận thông báo "[PGHHM] Đã duyệt: &lt;mã&gt;. Hạn trả mới: 05/10/2026."</t>
         </is>
       </c>
-      <c r="J119" s="15" t="inlineStr"/>
-      <c r="K119" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L119" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M119" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N119" s="15" t="inlineStr"/>
-      <c r="O119" s="16" t="inlineStr"/>
-      <c r="P119" s="16" t="inlineStr"/>
-      <c r="Q119" s="16" t="inlineStr"/>
-    </row>
-    <row r="120" ht="84" customHeight="1">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.007</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>Kế toán sửa Ngày hẹn trả mới rồi duyệt</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu N Chờ KT duyệt, Ngày hẹn trả mới 05/10/2026; hôm nay 30/09/2026, ngày trần 07/10/2026.</t>
-        </is>
-      </c>
-      <c r="G120" s="15" t="inlineStr">
-        <is>
-          <t>1. G mở N, đổi Ngày hẹn trả mới sang 03/10/2026.
-2. Bấm "KT duyệt", xác nhận.
-3. Mở phiếu mượn và Lịch sử thay đổi của N.</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr">
-        <is>
-          <t>Ngày hẹn trả mới: 03/10/2026</t>
-        </is>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>- Popup xác nhận nêu ngày 03/10/2026 (ngày vừa sửa).
-- Phiếu N Đã duyệt, Ngày hẹn trả mới = 03/10/2026.
-- Phiếu mượn có hạn trả 03/10/2026.
-- Lịch sử có dòng "Chỉnh sửa" (Ngày hẹn trả mới: 05/10/2026 sang 03/10/2026) nằm NGAY TRƯỚC dòng "Kế toán duyệt".</t>
-        </is>
-      </c>
-      <c r="J120" s="15" t="inlineStr"/>
-      <c r="K120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M120" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N120" s="15" t="inlineStr"/>
-      <c r="O120" s="16" t="inlineStr"/>
-      <c r="P120" s="16" t="inlineStr"/>
-      <c r="Q120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121" ht="37" customHeight="1">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.008</t>
-        </is>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>Kế toán xoá trống ô ngày rồi bấm duyệt</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F121" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu N Chờ KT duyệt.</t>
-        </is>
-      </c>
-      <c r="G121" s="15" t="inlineStr">
-        <is>
-          <t>1. G mở N, xoá ô Ngày hẹn trả mới (nếu xoá được).
-2. Bấm "KT duyệt".</t>
-        </is>
-      </c>
-      <c r="H121" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>- Báo lỗi dưới ô "Ngày hẹn trả mới – Bắt buộc phải chọn"; không mở popup xác nhận.
-- Phiếu không đổi trạng thái.</t>
-        </is>
-      </c>
-      <c r="J121" s="15" t="inlineStr"/>
-      <c r="K121" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L121" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M121" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N121" s="15" t="inlineStr"/>
-      <c r="O121" s="16" t="inlineStr"/>
-      <c r="P121" s="16" t="inlineStr"/>
-      <c r="Q121" s="16" t="inlineStr"/>
-    </row>
-    <row r="122" ht="46" customHeight="1">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.009</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>Trưởng phòng / Ban giám đốc không sửa được ngày</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu X Chờ TP duyệt, Ngày hẹn trả mới 05/10/2026.</t>
-        </is>
-      </c>
-      <c r="G122" s="15" t="inlineStr">
-        <is>
-          <t>1. E mở X, thử bấm vào ô Ngày hẹn trả mới.
-2. Dùng công cụ kiểm thử gửi lệnh duyệt kèm ngày 06/10/2026.</t>
-        </is>
-      </c>
-      <c r="H122" s="15" t="inlineStr">
-        <is>
-          <t>Ngày hẹn trả mới: 06/10/2026</t>
-        </is>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>- Bước 1: ô khoá, không mở được lịch.
-- Bước 2: phiếu vẫn được TP duyệt nhưng Ngày hẹn trả mới VẪN là 05/10/2026 (ngày gửi kèm bị bỏ qua).</t>
-        </is>
-      </c>
       <c r="J122" s="15" t="inlineStr"/>
       <c r="K122" s="16" t="inlineStr">
         <is>
@@ -8013,7 +8018,7 @@
       <c r="P122" s="16" t="inlineStr"/>
       <c r="Q122" s="16" t="inlineStr"/>
     </row>
-    <row r="123" ht="34" customHeight="1">
+    <row r="123" ht="92" customHeight="1">
       <c r="A123" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8026,38 +8031,42 @@
       </c>
       <c r="C123" s="16" t="inlineStr">
         <is>
-          <t>TC_06.010</t>
+          <t>TC_06.007</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
         <is>
-          <t>Hủy ở popup xác nhận duyệt</t>
+          <t>Kế toán sửa Ngày hẹn trả mới rồi duyệt</t>
         </is>
       </c>
       <c r="E123" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>Phiếu X Chờ TP duyệt.</t>
+          <t>Phiếu N Chờ KT duyệt, Ngày hẹn trả mới 05/10/2026; hôm nay 30/09/2026, ngày trần 07/10/2026.</t>
         </is>
       </c>
       <c r="G123" s="15" t="inlineStr">
         <is>
-          <t>1. E bấm "TP duyệt".
-2. Ở popup xác nhận chọn huỷ / đóng.</t>
+          <t>1. G mở N, đổi Ngày hẹn trả mới sang 03/10/2026.
+2. Bấm "KT duyệt", xác nhận.
+3. Mở phiếu mượn và Lịch sử thay đổi của N.</t>
         </is>
       </c>
       <c r="H123" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ngày hẹn trả mới: 03/10/2026</t>
         </is>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
-          <t>- Popup đóng, vẫn ở màn chi tiết; phiếu vẫn Chờ TP duyệt.</t>
+          <t>- Popup xác nhận nêu ngày 03/10/2026 (ngày vừa sửa).
+- Phiếu N Đã duyệt, Ngày hẹn trả mới = 03/10/2026.
+- Phiếu mượn có hạn trả 03/10/2026.
+- Lịch sử có dòng "Thay đổi thông tin" (Ngày hẹn trả mới: 05/10/2026 sang 03/10/2026) nằm NGAY DƯỚI dòng "Kế toán duyệt" (xảy ra trước).</t>
         </is>
       </c>
       <c r="J123" s="15" t="inlineStr"/>
@@ -8081,7 +8090,7 @@
       <c r="P123" s="16" t="inlineStr"/>
       <c r="Q123" s="16" t="inlineStr"/>
     </row>
-    <row r="124" ht="125" customHeight="1">
+    <row r="124" ht="37" customHeight="1">
       <c r="A124" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8094,37 +8103,243 @@
       </c>
       <c r="C124" s="16" t="inlineStr">
         <is>
+          <t>TC_06.008</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>Kế toán xoá trống ô ngày rồi bấm duyệt</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu N Chờ KT duyệt.</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="inlineStr">
+        <is>
+          <t>1. G mở N, xoá ô Ngày hẹn trả mới (nếu xoá được).
+2. Bấm "KT duyệt".</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>- Báo lỗi dưới ô "Ngày hẹn trả mới – Bắt buộc phải chọn"; không mở popup xác nhận.
+- Phiếu không đổi trạng thái.</t>
+        </is>
+      </c>
+      <c r="J124" s="15" t="inlineStr"/>
+      <c r="K124" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L124" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N124" s="15" t="inlineStr"/>
+      <c r="O124" s="16" t="inlineStr"/>
+      <c r="P124" s="16" t="inlineStr"/>
+      <c r="Q124" s="16" t="inlineStr"/>
+    </row>
+    <row r="125" ht="46" customHeight="1">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>TC_06.009</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>Trưởng phòng / Ban giám đốc không sửa được ngày</t>
+        </is>
+      </c>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F125" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu X Chờ TP duyệt, Ngày hẹn trả mới 05/10/2026.</t>
+        </is>
+      </c>
+      <c r="G125" s="15" t="inlineStr">
+        <is>
+          <t>1. E mở X, thử bấm vào ô Ngày hẹn trả mới.
+2. Dùng công cụ kiểm thử gửi lệnh duyệt kèm ngày 06/10/2026.</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="inlineStr">
+        <is>
+          <t>Ngày hẹn trả mới: 06/10/2026</t>
+        </is>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>- Bước 1: ô khoá, không mở được lịch.
+- Bước 2: phiếu vẫn được TP duyệt nhưng Ngày hẹn trả mới VẪN là 05/10/2026 (ngày gửi kèm bị bỏ qua).</t>
+        </is>
+      </c>
+      <c r="J125" s="15" t="inlineStr"/>
+      <c r="K125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N125" s="15" t="inlineStr"/>
+      <c r="O125" s="16" t="inlineStr"/>
+      <c r="P125" s="16" t="inlineStr"/>
+      <c r="Q125" s="16" t="inlineStr"/>
+    </row>
+    <row r="126" ht="34" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>TC_06.010</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>Hủy ở popup xác nhận duyệt</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu X Chờ TP duyệt.</t>
+        </is>
+      </c>
+      <c r="G126" s="15" t="inlineStr">
+        <is>
+          <t>1. E bấm "TP duyệt".
+2. Ở popup xác nhận chọn huỷ / đóng.</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>- Popup đóng, vẫn ở màn chi tiết; phiếu vẫn Chờ TP duyệt.</t>
+        </is>
+      </c>
+      <c r="J126" s="15" t="inlineStr"/>
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N126" s="15" t="inlineStr"/>
+      <c r="O126" s="16" t="inlineStr"/>
+      <c r="P126" s="16" t="inlineStr"/>
+      <c r="Q126" s="16" t="inlineStr"/>
+    </row>
+    <row r="127" ht="125" customHeight="1">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
           <t>TC_06.011</t>
         </is>
       </c>
-      <c r="D124" s="15" t="inlineStr">
+      <c r="D127" s="15" t="inlineStr">
         <is>
           <t>Từ chối từ màn chi tiết</t>
         </is>
       </c>
-      <c r="E124" s="16" t="inlineStr">
+      <c r="E127" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F124" s="15" t="inlineStr">
+      <c r="F127" s="15" t="inlineStr">
         <is>
           <t>Phiếu X Chờ TP duyệt; E quản lý phòng của X.</t>
         </is>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G127" s="15" t="inlineStr">
         <is>
           <t>1. E mở X, bấm "Từ chối".
 2. Nhập lý do.
 3. Bấm "Xác nhận từ chối".</t>
         </is>
       </c>
-      <c r="H124" s="15" t="inlineStr">
+      <c r="H127" s="15" t="inlineStr">
         <is>
           <t>Lý do từ chối: Chưa trả hàng kỳ trước</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I127" s="15" t="inlineStr">
         <is>
           <t>- Popup tiêu đề "Từ chối yêu cầu gia hạn: &lt;mã&gt;", ô "Lý do từ chối" bắt buộc, dòng nhắc phiếu sẽ chuyển sang Không duyệt và người lập phải tạo phiếu mới.
 - Thông báo "Đã từ chối yêu cầu gia hạn hàng mượn."
@@ -8133,214 +8348,6 @@
 - Người lập nhận thông báo "[PGHHM] Từ chối: &lt;mã&gt;. Lý do: Chưa trả hàng kỳ trước"</t>
         </is>
       </c>
-      <c r="J124" s="15" t="inlineStr"/>
-      <c r="K124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M124" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N124" s="15" t="inlineStr"/>
-      <c r="O124" s="16" t="inlineStr"/>
-      <c r="P124" s="16" t="inlineStr"/>
-      <c r="Q124" s="16" t="inlineStr"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.012</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>Từ chối từ menu dòng ở danh sách</t>
-        </is>
-      </c>
-      <c r="E125" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F125" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu Y Chờ KT duyệt; G là Kế toán kho cùng công ty.</t>
-        </is>
-      </c>
-      <c r="G125" s="15" t="inlineStr">
-        <is>
-          <t>1. Ở danh sách, chọn Hành động &gt; Từ chối ở dòng Y.
-2. Nhập lý do, bấm "Xác nhận từ chối".</t>
-        </is>
-      </c>
-      <c r="H125" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối: Sai phiếu mượn</t>
-        </is>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>- Popup đóng, danh sách tự nạp lại, vẫn ở màn danh sách.
-- Dòng Y thành Không duyệt, menu Hành động chỉ còn In, Lịch sử.
-- Người duyệt / Ngày duyệt của Y hiện G và thời điểm từ chối.</t>
-        </is>
-      </c>
-      <c r="J125" s="15" t="inlineStr"/>
-      <c r="K125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M125" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N125" s="15" t="inlineStr"/>
-      <c r="O125" s="16" t="inlineStr"/>
-      <c r="P125" s="16" t="inlineStr"/>
-      <c r="Q125" s="16" t="inlineStr"/>
-    </row>
-    <row r="126" ht="43" customHeight="1">
-      <c r="A126" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B126" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.013</t>
-        </is>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>Từ chối ở cấp Ban giám đốc</t>
-        </is>
-      </c>
-      <c r="E126" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F126" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu M Chờ BGĐ duyệt.</t>
-        </is>
-      </c>
-      <c r="G126" s="15" t="inlineStr">
-        <is>
-          <t>1. F từ chối M với lý do.</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối: Giá trị còn nợ quá lớn</t>
-        </is>
-      </c>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t>- M ở trạng thái Không duyệt.
-- Khối Lịch sử duyệt: dòng Trưởng phòng (đã duyệt) và dòng Ban giám đốc có nhãn "Từ chối" kèm lý do.</t>
-        </is>
-      </c>
-      <c r="J126" s="15" t="inlineStr"/>
-      <c r="K126" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L126" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M126" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N126" s="15" t="inlineStr"/>
-      <c r="O126" s="16" t="inlineStr"/>
-      <c r="P126" s="16" t="inlineStr"/>
-      <c r="Q126" s="16" t="inlineStr"/>
-    </row>
-    <row r="127" ht="39" customHeight="1">
-      <c r="A127" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B127" s="15" t="inlineStr">
-        <is>
-          <t>DUYỆT &amp; TỪ CHỐI</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>TC_06.014</t>
-        </is>
-      </c>
-      <c r="D127" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối bắt buộc</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F127" s="15" t="inlineStr">
-        <is>
-          <t>Đang mở popup Từ chối.</t>
-        </is>
-      </c>
-      <c r="G127" s="15" t="inlineStr">
-        <is>
-          <t>1. Để trống ô lý do, bấm "Xác nhận từ chối".
-2. Nhập toàn khoảng trắng, bấm lại.</t>
-        </is>
-      </c>
-      <c r="H127" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối: (trống)
-Lý do từ chối: (5 dấu cách)</t>
-        </is>
-      </c>
-      <c r="I127" s="15" t="inlineStr">
-        <is>
-          <t>- Cả hai lần đều báo "Lý do từ chối – Bắt buộc phải nhập", ô viền đỏ.
-- Popup không đóng, phiếu không đổi trạng thái.</t>
-        </is>
-      </c>
       <c r="J127" s="15" t="inlineStr"/>
       <c r="K127" s="16" t="inlineStr">
         <is>
@@ -8362,7 +8369,7 @@
       <c r="P127" s="16" t="inlineStr"/>
       <c r="Q127" s="16" t="inlineStr"/>
     </row>
-    <row r="128" ht="34" customHeight="1">
+    <row r="128" ht="60" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8375,37 +8382,40 @@
       </c>
       <c r="C128" s="16" t="inlineStr">
         <is>
-          <t>TC_06.015</t>
+          <t>TC_06.012</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Đóng popup Từ chối không lưu</t>
+          <t>Từ chối từ menu dòng ở danh sách</t>
         </is>
       </c>
       <c r="E128" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
-          <t>Đang mở popup Từ chối, đã gõ lý do.</t>
+          <t>Phiếu Y Chờ KT duyệt; G là Kế toán kho cùng công ty.</t>
         </is>
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm "Đóng".</t>
+          <t>1. Ở danh sách, chọn Hành động &gt; Từ chối ở dòng Y.
+2. Nhập lý do, bấm "Xác nhận từ chối".</t>
         </is>
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lý do từ chối: Sai phiếu mượn</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>- Popup đóng, phiếu vẫn giữ trạng thái chờ duyệt.</t>
+          <t>- Popup đóng, danh sách tự nạp lại, vẫn ở màn danh sách.
+- Dòng Y thành Không duyệt, menu Hành động chỉ còn In, Lịch sử.
+- Người duyệt / Ngày duyệt của Y hiện G và thời điểm từ chối.</t>
         </is>
       </c>
       <c r="J128" s="15" t="inlineStr"/>
@@ -8429,7 +8439,7 @@
       <c r="P128" s="16" t="inlineStr"/>
       <c r="Q128" s="16" t="inlineStr"/>
     </row>
-    <row r="129" ht="34" customHeight="1">
+    <row r="129" ht="43" customHeight="1">
       <c r="A129" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8442,39 +8452,38 @@
       </c>
       <c r="C129" s="16" t="inlineStr">
         <is>
-          <t>TC_06.016</t>
+          <t>TC_06.013</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>Phiếu Không duyệt không duyệt tiếp được</t>
+          <t>Từ chối ở cấp Ban giám đốc</t>
         </is>
       </c>
       <c r="E129" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>Phiếu X đã Không duyệt.</t>
+          <t>Phiếu M Chờ BGĐ duyệt.</t>
         </is>
       </c>
       <c r="G129" s="15" t="inlineStr">
         <is>
-          <t>1. Super Admin mở X.
-2. Dùng công cụ kiểm thử gọi chức năng duyệt X.</t>
+          <t>1. F từ chối M với lý do.</t>
         </is>
       </c>
       <c r="H129" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lý do từ chối: Giá trị còn nợ quá lớn</t>
         </is>
       </c>
       <c r="I129" s="15" t="inlineStr">
         <is>
-          <t>- Không có nút duyệt / từ chối.
-- Gọi thẳng: phần mềm báo "Phiếu không ở trạng thái chờ duyệt."</t>
+          <t>- M ở trạng thái Không duyệt.
+- Khối Lịch sử duyệt: dòng Trưởng phòng (đã duyệt) và dòng Ban giám đốc có nhãn "Từ chối" kèm lý do.</t>
         </is>
       </c>
       <c r="J129" s="15" t="inlineStr"/>
@@ -8498,7 +8507,7 @@
       <c r="P129" s="16" t="inlineStr"/>
       <c r="Q129" s="16" t="inlineStr"/>
     </row>
-    <row r="130" ht="34" customHeight="1">
+    <row r="130" ht="39" customHeight="1">
       <c r="A130" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8511,37 +8520,40 @@
       </c>
       <c r="C130" s="16" t="inlineStr">
         <is>
-          <t>TC_06.017</t>
+          <t>TC_06.014</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Phiếu Đã duyệt không duyệt lại được</t>
+          <t>Lý do từ chối bắt buộc</t>
         </is>
       </c>
       <c r="E130" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
-          <t>Phiếu N Đã duyệt.</t>
+          <t>Đang mở popup Từ chối.</t>
         </is>
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gọi chức năng duyệt N bằng tài khoản Kế toán kho.</t>
+          <t>1. Để trống ô lý do, bấm "Xác nhận từ chối".
+2. Nhập toàn khoảng trắng, bấm lại.</t>
         </is>
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lý do từ chối: (trống)
+Lý do từ chối: (5 dấu cách)</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>- Phần mềm báo "Phiếu không ở trạng thái chờ duyệt."; phiếu mượn không đổi hạn trả.</t>
+          <t>- Cả hai lần đều báo "Lý do từ chối – Bắt buộc phải nhập", ô viền đỏ.
+- Popup không đóng, phiếu không đổi trạng thái.</t>
         </is>
       </c>
       <c r="J130" s="15" t="inlineStr"/>
@@ -8565,7 +8577,7 @@
       <c r="P130" s="16" t="inlineStr"/>
       <c r="Q130" s="16" t="inlineStr"/>
     </row>
-    <row r="131" ht="38" customHeight="1">
+    <row r="131" ht="34" customHeight="1">
       <c r="A131" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8578,39 +8590,37 @@
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>TC_06.018</t>
+          <t>TC_06.015</t>
         </is>
       </c>
       <c r="D131" s="15" t="inlineStr">
         <is>
-          <t>Kế toán sửa ngày vượt trần</t>
+          <t>Đóng popup Từ chối không lưu</t>
         </is>
       </c>
       <c r="E131" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F131" s="15" t="inlineStr">
         <is>
-          <t>Hôm nay 30/09/2026, ngày trần 07/10/2026. Phiếu N Chờ KT duyệt.</t>
+          <t>Đang mở popup Từ chối, đã gõ lý do.</t>
         </is>
       </c>
       <c r="G131" s="15" t="inlineStr">
         <is>
-          <t>1. G mở lịch ô Ngày hẹn trả mới, thử chọn 08/10/2026.
-2. Dùng công cụ kiểm thử gửi lệnh duyệt kèm ngày 08/10/2026.</t>
+          <t>1. Bấm "Đóng".</t>
         </is>
       </c>
       <c r="H131" s="15" t="inlineStr">
         <is>
-          <t>Ngày hẹn trả mới: 08/10/2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I131" s="15" t="inlineStr">
         <is>
-          <t>- Bước 1: ngày 08/10 bị mờ, không chọn được.
-- Bước 2: báo "Không thể mượn quá 07/10/2026"; phiếu vẫn Chờ KT duyệt.</t>
+          <t>- Popup đóng, phiếu vẫn giữ trạng thái chờ duyệt.</t>
         </is>
       </c>
       <c r="J131" s="15" t="inlineStr"/>
@@ -8634,7 +8644,7 @@
       <c r="P131" s="16" t="inlineStr"/>
       <c r="Q131" s="16" t="inlineStr"/>
     </row>
-    <row r="132" ht="60" customHeight="1">
+    <row r="132" ht="34" customHeight="1">
       <c r="A132" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8647,12 +8657,12 @@
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
-          <t>TC_06.019</t>
+          <t>TC_06.016</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn đã được gia hạn xen giữa bởi phiếu khác</t>
+          <t>Phiếu Không duyệt không duyệt tiếp được</t>
         </is>
       </c>
       <c r="E132" s="16" t="inlineStr">
@@ -8662,12 +8672,13 @@
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn M có hạn 23/09. Phiếu gia hạn A1 (ngày mới 03/10) đã Đã duyệt nên hạn của M nay là 03/10. Phiếu gia hạn A2 cũ của M (ngày mới 02/10) vẫn Chờ KT duyệt (lập bên cổng ERP).</t>
+          <t>Phiếu X đã Không duyệt.</t>
         </is>
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>1. Kế toán mở A2, bấm "KT duyệt" giữ nguyên ngày 02/10.</t>
+          <t>1. Super Admin mở X.
+2. Dùng công cụ kiểm thử gọi chức năng duyệt X.</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
@@ -8677,8 +8688,8 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>- Báo lỗi dưới ô ngày "Phải sau ngày hẹn trả hiện tại (03/10/2026)".
-- A2 vẫn Chờ KT duyệt; hạn của M vẫn 03/10.</t>
+          <t>- Không có nút duyệt / từ chối.
+- Gọi thẳng: phần mềm báo "Phiếu không ở trạng thái chờ duyệt."</t>
         </is>
       </c>
       <c r="J132" s="15" t="inlineStr"/>
@@ -8715,12 +8726,12 @@
       </c>
       <c r="C133" s="16" t="inlineStr">
         <is>
-          <t>TC_06.020</t>
+          <t>TC_06.017</t>
         </is>
       </c>
       <c r="D133" s="15" t="inlineStr">
         <is>
-          <t>Người duyệt sai phòng không thấy nút duyệt ở danh sách</t>
+          <t>Phiếu Đã duyệt không duyệt lại được</t>
         </is>
       </c>
       <c r="E133" s="16" t="inlineStr">
@@ -8730,12 +8741,12 @@
       </c>
       <c r="F133" s="15" t="inlineStr">
         <is>
-          <t>E quản lý P1; phiếu Y Chờ TP duyệt thuộc P2.</t>
+          <t>Phiếu N Đã duyệt.</t>
         </is>
       </c>
       <c r="G133" s="15" t="inlineStr">
         <is>
-          <t>1. E xem dòng Y (nếu nhìn thấy trong phạm vi xem).</t>
+          <t>1. Dùng công cụ kiểm thử gọi chức năng duyệt N bằng tài khoản Kế toán kho.</t>
         </is>
       </c>
       <c r="H133" s="15" t="inlineStr">
@@ -8745,7 +8756,7 @@
       </c>
       <c r="I133" s="15" t="inlineStr">
         <is>
-          <t>- Menu Hành động dòng Y không có Duyệt, Từ chối.</t>
+          <t>- Phần mềm báo "Phiếu không ở trạng thái chờ duyệt."; phiếu mượn không đổi hạn trả.</t>
         </is>
       </c>
       <c r="J133" s="15" t="inlineStr"/>
@@ -8769,7 +8780,7 @@
       <c r="P133" s="16" t="inlineStr"/>
       <c r="Q133" s="16" t="inlineStr"/>
     </row>
-    <row r="134" ht="34" customHeight="1">
+    <row r="134" ht="38" customHeight="1">
       <c r="A134" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8782,37 +8793,39 @@
       </c>
       <c r="C134" s="16" t="inlineStr">
         <is>
-          <t>TC_06.021</t>
+          <t>TC_06.018</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Super Admin duyệt được mọi cấp</t>
+          <t>Kế toán sửa ngày vượt trần</t>
         </is>
       </c>
       <c r="E134" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>Super Admin cùng công ty với phiếu X Chờ TP duyệt thuộc phòng Super Admin không quản lý.</t>
+          <t>Hôm nay 30/09/2026, ngày trần 07/10/2026. Phiếu N Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>1. Super Admin mở X, bấm "TP duyệt".</t>
+          <t>1. G mở lịch ô Ngày hẹn trả mới, thử chọn 08/10/2026.
+2. Dùng công cụ kiểm thử gửi lệnh duyệt kèm ngày 08/10/2026.</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ngày hẹn trả mới: 08/10/2026</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>- Duyệt thành công (không bị ràng buộc phòng ban quản lý).</t>
+          <t>- Bước 1: ngày 08/10 bị mờ, không chọn được.
+- Bước 2: báo "Không thể mượn quá 07/10/2026"; phiếu vẫn Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="J134" s="15" t="inlineStr"/>
@@ -8836,7 +8849,7 @@
       <c r="P134" s="16" t="inlineStr"/>
       <c r="Q134" s="16" t="inlineStr"/>
     </row>
-    <row r="135" ht="34" customHeight="1">
+    <row r="135" ht="60" customHeight="1">
       <c r="A135" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8849,27 +8862,27 @@
       </c>
       <c r="C135" s="16" t="inlineStr">
         <is>
-          <t>TC_06.022</t>
+          <t>TC_06.019</t>
         </is>
       </c>
       <c r="D135" s="15" t="inlineStr">
         <is>
-          <t>Nhãn nút duyệt đổi theo cấp</t>
+          <t>Phiếu mượn đã được gia hạn xen giữa bởi phiếu khác</t>
         </is>
       </c>
       <c r="E135" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F135" s="15" t="inlineStr">
         <is>
-          <t>Ba phiếu ở ba trạng thái chờ, người mở có quyền đúng cấp.</t>
+          <t>Phiếu mượn M có hạn 23/09. Phiếu gia hạn A1 (ngày mới 03/10) đã Đã duyệt nên hạn của M nay là 03/10. Phiếu gia hạn A2 cũ của M (ngày mới 02/10) vẫn Chờ KT duyệt (lập bên cổng ERP).</t>
         </is>
       </c>
       <c r="G135" s="15" t="inlineStr">
         <is>
-          <t>1. Mở lần lượt từng phiếu.</t>
+          <t>1. Kế toán mở A2, bấm "KT duyệt" giữ nguyên ngày 02/10.</t>
         </is>
       </c>
       <c r="H135" s="15" t="inlineStr">
@@ -8879,9 +8892,8 @@
       </c>
       <c r="I135" s="15" t="inlineStr">
         <is>
-          <t>- Chờ TP duyệt: nút "TP duyệt".
-- Chờ BGĐ duyệt: nút "BGĐ duyệt".
-- Chờ KT duyệt: nút "KT duyệt".</t>
+          <t>- Báo lỗi dưới ô ngày "Phải sau ngày hẹn trả hiện tại (03/10/2026)".
+- A2 vẫn Chờ KT duyệt; hạn của M vẫn 03/10.</t>
         </is>
       </c>
       <c r="J135" s="15" t="inlineStr"/>
@@ -8905,30 +8917,74 @@
       <c r="P135" s="16" t="inlineStr"/>
       <c r="Q135" s="16" t="inlineStr"/>
     </row>
-    <row r="136" ht="26" customHeight="1">
-      <c r="A136" s="13" t="n"/>
-      <c r="B136" s="13" t="n"/>
-      <c r="C136" s="14" t="inlineStr">
-        <is>
-          <t>VII. CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
-      <c r="J136" s="4" t="n"/>
-      <c r="K136" s="4" t="n"/>
-      <c r="L136" s="4" t="n"/>
-      <c r="M136" s="4" t="n"/>
-      <c r="N136" s="4" t="n"/>
-      <c r="O136" s="4" t="n"/>
-      <c r="P136" s="4" t="n"/>
-      <c r="Q136" s="5" t="n"/>
-    </row>
-    <row r="137" ht="61" customHeight="1">
+    <row r="136" ht="34" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>TC_06.020</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>Người duyệt sai phòng không thấy nút duyệt ở danh sách</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F136" s="15" t="inlineStr">
+        <is>
+          <t>E quản lý P1; phiếu Y Chờ TP duyệt thuộc P2.</t>
+        </is>
+      </c>
+      <c r="G136" s="15" t="inlineStr">
+        <is>
+          <t>1. E xem dòng Y (nếu nhìn thấy trong phạm vi xem).</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>- Menu Hành động dòng Y không có Duyệt, Từ chối.</t>
+        </is>
+      </c>
+      <c r="J136" s="15" t="inlineStr"/>
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N136" s="15" t="inlineStr"/>
+      <c r="O136" s="16" t="inlineStr"/>
+      <c r="P136" s="16" t="inlineStr"/>
+      <c r="Q136" s="16" t="inlineStr"/>
+    </row>
+    <row r="137" ht="34" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -8936,34 +8992,32 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
         </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
         <is>
-          <t>TC_07.001</t>
+          <t>TC_06.021</t>
         </is>
       </c>
       <c r="D137" s="15" t="inlineStr">
         <is>
-          <t>Trưởng phòng bị chặn duyệt khi phòng có nhân viên mượn hàng quá hạn</t>
+          <t>Super Admin duyệt được mọi cấp</t>
         </is>
       </c>
       <c r="E137" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F137" s="15" t="inlineStr">
         <is>
-          <t>Cấu hình chặn thao tác "Duyệt gia hạn hàng mượn" đang BẬT cho nhóm hàng mượn quá hạn.
-E quản lý P1; nhân viên V thuộc P1 đang có hàng mượn đã quá hạn trả.
-Phiếu X Chờ TP duyệt thuộc P1.</t>
+          <t>Super Admin cùng công ty với phiếu X Chờ TP duyệt thuộc phòng Super Admin không quản lý.</t>
         </is>
       </c>
       <c r="G137" s="15" t="inlineStr">
         <is>
-          <t>1. E mở X, bấm "TP duyệt", xác nhận.</t>
+          <t>1. Super Admin mở X, bấm "TP duyệt".</t>
         </is>
       </c>
       <c r="H137" s="15" t="inlineStr">
@@ -8973,8 +9027,7 @@
       </c>
       <c r="I137" s="15" t="inlineStr">
         <is>
-          <t>- Phần mềm báo "Phòng ban bạn quản lý có nhân viên hàng mượn quá hạn. Không thể thực hiện thao tác này."
-- X vẫn Chờ TP duyệt; không có dòng lịch sử mới.</t>
+          <t>- Duyệt thành công (không bị ràng buộc phòng ban quản lý).</t>
         </is>
       </c>
       <c r="J137" s="15" t="inlineStr"/>
@@ -9006,32 +9059,32 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
         </is>
       </c>
       <c r="C138" s="16" t="inlineStr">
         <is>
-          <t>TC_07.002</t>
+          <t>TC_06.022</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Không còn nhân viên quá hạn thì duyệt bình thường</t>
+          <t>Nhãn nút duyệt đổi theo cấp</t>
         </is>
       </c>
       <c r="E138" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F138" s="15" t="inlineStr">
         <is>
-          <t>Như TC_07.001, sau đó V đã trả hàng (hết quá hạn).</t>
+          <t>Ba phiếu ở ba trạng thái chờ, người mở có quyền đúng cấp.</t>
         </is>
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>1. E duyệt lại X.</t>
+          <t>1. Mở lần lượt từng phiếu.</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
@@ -9041,7 +9094,9 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>- Duyệt thành công, X sang cấp tiếp theo.</t>
+          <t>- Chờ TP duyệt: nút "TP duyệt".
+- Chờ BGĐ duyệt: nút "BGĐ duyệt".
+- Chờ KT duyệt: nút "KT duyệt".</t>
         </is>
       </c>
       <c r="J138" s="15" t="inlineStr"/>
@@ -9065,7 +9120,7 @@
       <c r="P138" s="16" t="inlineStr"/>
       <c r="Q138" s="16" t="inlineStr"/>
     </row>
-    <row r="139" ht="34" customHeight="1">
+    <row r="139" ht="77" customHeight="1">
       <c r="A139" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9073,17 +9128,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
+          <t>DUYỆT &amp; TỪ CHỐI</t>
         </is>
       </c>
       <c r="C139" s="16" t="inlineStr">
         <is>
-          <t>TC_07.003</t>
+          <t>TC_06.023</t>
         </is>
       </c>
       <c r="D139" s="15" t="inlineStr">
         <is>
-          <t>Tắt cấu hình chặn thì không chặn</t>
+          <t>Công ty chưa khai hạn mức giá trị hàng mượn</t>
         </is>
       </c>
       <c r="E139" s="16" t="inlineStr">
@@ -9093,12 +9148,12 @@
       </c>
       <c r="F139" s="15" t="inlineStr">
         <is>
-          <t>Như TC_07.001 nhưng cấu hình chặn "Duyệt gia hạn hàng mượn" đang TẮT.</t>
+          <t>Công ty 3 để TRỐNG hạn mức giá trị hàng mượn. Phiếu X (công ty 3) gắn phiếu mượn còn nợ 1,500,000.</t>
         </is>
       </c>
       <c r="G139" s="15" t="inlineStr">
         <is>
-          <t>1. E duyệt X.</t>
+          <t>1. Trưởng phòng cùng công ty duyệt X.</t>
         </is>
       </c>
       <c r="H139" s="15" t="inlineStr">
@@ -9108,7 +9163,8 @@
       </c>
       <c r="I139" s="15" t="inlineStr">
         <is>
-          <t>- Duyệt thành công dù phòng còn nhân viên quá hạn.</t>
+          <t>- X sang Chờ BGĐ duyệt, thông báo "Yêu cầu đã được chuyển đến Ban giám đốc."
+- Lưu ý: hạn mức trống được coi là 0, nên mọi phiếu mượn còn nợ đều phải qua Ban giám đốc. Muốn bỏ bước này phải khai hạn mức cho công ty (Redmine #11550).</t>
         </is>
       </c>
       <c r="J139" s="15" t="inlineStr"/>
@@ -9132,107 +9188,65 @@
       <c r="P139" s="16" t="inlineStr"/>
       <c r="Q139" s="16" t="inlineStr"/>
     </row>
-    <row r="140" ht="34" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B140" s="15" t="inlineStr">
+    <row r="140" ht="26" customHeight="1">
+      <c r="A140" s="13" t="n"/>
+      <c r="B140" s="13" t="n"/>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>VII. CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
+      <c r="P140" s="4" t="n"/>
+      <c r="Q140" s="5" t="n"/>
+    </row>
+    <row r="141" ht="77" customHeight="1">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
         <is>
           <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
         </is>
       </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>TC_07.004</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>Từ chối không bị chặn quá hạn</t>
-        </is>
-      </c>
-      <c r="E140" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F140" s="15" t="inlineStr">
-        <is>
-          <t>Như TC_07.001.</t>
-        </is>
-      </c>
-      <c r="G140" s="15" t="inlineStr">
-        <is>
-          <t>1. E bấm "Từ chối" phiếu X, nhập lý do, xác nhận.</t>
-        </is>
-      </c>
-      <c r="H140" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối: Nhắc trả hàng quá hạn trước</t>
-        </is>
-      </c>
-      <c r="I140" s="15" t="inlineStr">
-        <is>
-          <t>- Từ chối thành công, X thành Không duyệt.</t>
-        </is>
-      </c>
-      <c r="J140" s="15" t="inlineStr"/>
-      <c r="K140" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L140" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M140" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N140" s="15" t="inlineStr"/>
-      <c r="O140" s="16" t="inlineStr"/>
-      <c r="P140" s="16" t="inlineStr"/>
-      <c r="Q140" s="16" t="inlineStr"/>
-    </row>
-    <row r="141" ht="34" customHeight="1">
-      <c r="A141" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B141" s="15" t="inlineStr">
-        <is>
-          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
-        </is>
-      </c>
       <c r="C141" s="16" t="inlineStr">
         <is>
-          <t>TC_07.005</t>
+          <t>TC_07.001</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
         <is>
-          <t>Super Admin không bị chặn</t>
+          <t>Trưởng phòng bị chặn duyệt khi phòng có nhân viên mượn hàng quá hạn</t>
         </is>
       </c>
       <c r="E141" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F141" s="15" t="inlineStr">
         <is>
-          <t>Super Admin quản lý phòng P1 đang có nhân viên quá hạn.</t>
+          <t>Cấu hình chặn thao tác "Duyệt gia hạn hàng mượn" đang BẬT cho nhóm hàng mượn quá hạn.
+E quản lý P1; nhân viên V thuộc P1 đang có hàng mượn đã quá hạn trả.
+Phiếu X Chờ TP duyệt thuộc P1.</t>
         </is>
       </c>
       <c r="G141" s="15" t="inlineStr">
         <is>
-          <t>1. Super Admin duyệt phiếu Chờ TP duyệt của P1.</t>
+          <t>1. E mở X, bấm "TP duyệt", xác nhận.</t>
         </is>
       </c>
       <c r="H141" s="15" t="inlineStr">
@@ -9242,7 +9256,9 @@
       </c>
       <c r="I141" s="15" t="inlineStr">
         <is>
-          <t>- Duyệt thành công.</t>
+          <t>- Phần mềm báo "Phòng ban bạn quản lý có nhân viên hàng mượn quá hạn. Không thể thực hiện thao tác này."
+- Đồng thời mở cửa sổ liệt kê từng nhân viên đang quá hạn và loại hàng quá hạn.
+- X vẫn Chờ TP duyệt; không có dòng lịch sử mới.</t>
         </is>
       </c>
       <c r="J141" s="15" t="inlineStr"/>
@@ -9266,7 +9282,7 @@
       <c r="P141" s="16" t="inlineStr"/>
       <c r="Q141" s="16" t="inlineStr"/>
     </row>
-    <row r="142" ht="59" customHeight="1">
+    <row r="142" ht="34" customHeight="1">
       <c r="A142" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9279,27 +9295,27 @@
       </c>
       <c r="C142" s="16" t="inlineStr">
         <is>
-          <t>TC_07.006</t>
+          <t>TC_07.002</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>Kế toán / Ban giám đốc quản lý phòng có nhân viên quá hạn</t>
+          <t>Không còn nhân viên quá hạn thì duyệt bình thường</t>
         </is>
       </c>
       <c r="E142" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>Kế toán G (quyền Kế toán kho) đồng thời được phân công quản lý phòng P3; P3 có nhân viên mượn hàng quá hạn. Cấu hình chặn đang bật. Phiếu N Chờ KT duyệt.</t>
+          <t>Như TC_07.001, sau đó V đã trả hàng (hết quá hạn).</t>
         </is>
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>1. G bấm "KT duyệt" phiếu N.</t>
+          <t>1. E duyệt lại X.</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
@@ -9309,8 +9325,7 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>- Phần mềm CŨNG chặn với cùng thông báo như TC_07.001.
-- Lưu ý: chốt chặn gắn trên thao tác duyệt nói chung, xét theo phòng ban NGƯỜI DUYỆT quản lý, không riêng cấp Trưởng phòng.</t>
+          <t>- Duyệt thành công, X sang cấp tiếp theo.</t>
         </is>
       </c>
       <c r="J142" s="15" t="inlineStr"/>
@@ -9334,30 +9349,74 @@
       <c r="P142" s="16" t="inlineStr"/>
       <c r="Q142" s="16" t="inlineStr"/>
     </row>
-    <row r="143" ht="26" customHeight="1">
-      <c r="A143" s="13" t="n"/>
-      <c r="B143" s="13" t="n"/>
-      <c r="C143" s="14" t="inlineStr">
-        <is>
-          <t>VIII. IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="4" t="n"/>
-      <c r="H143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
-      <c r="J143" s="4" t="n"/>
-      <c r="K143" s="4" t="n"/>
-      <c r="L143" s="4" t="n"/>
-      <c r="M143" s="4" t="n"/>
-      <c r="N143" s="4" t="n"/>
-      <c r="O143" s="4" t="n"/>
-      <c r="P143" s="4" t="n"/>
-      <c r="Q143" s="5" t="n"/>
-    </row>
-    <row r="144" ht="140" customHeight="1">
+    <row r="143" ht="34" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="inlineStr">
+        <is>
+          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>TC_07.003</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>Tắt cấu hình chặn thì không chặn</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F143" s="15" t="inlineStr">
+        <is>
+          <t>Như TC_07.001 nhưng cấu hình chặn "Duyệt gia hạn hàng mượn" đang TẮT.</t>
+        </is>
+      </c>
+      <c r="G143" s="15" t="inlineStr">
+        <is>
+          <t>1. E duyệt X.</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I143" s="15" t="inlineStr">
+        <is>
+          <t>- Duyệt thành công dù phòng còn nhân viên quá hạn.</t>
+        </is>
+      </c>
+      <c r="J143" s="15" t="inlineStr"/>
+      <c r="K143" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L143" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N143" s="15" t="inlineStr"/>
+      <c r="O143" s="16" t="inlineStr"/>
+      <c r="P143" s="16" t="inlineStr"/>
+      <c r="Q143" s="16" t="inlineStr"/>
+    </row>
+    <row r="144" ht="34" customHeight="1">
       <c r="A144" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9365,45 +9424,42 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>IN &amp; XUẤT EXCEL</t>
+          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
         </is>
       </c>
       <c r="C144" s="16" t="inlineStr">
         <is>
-          <t>TC_08.001</t>
+          <t>TC_07.004</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>In một phiếu từ màn chi tiết</t>
+          <t>Từ chối không bị chặn quá hạn</t>
         </is>
       </c>
       <c r="E144" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
-          <t>Phiếu N Đã duyệt, qua đủ 3 cấp, phiếu mượn có 3 mặt hàng.</t>
+          <t>Như TC_07.001.</t>
         </is>
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết N, bấm "In".</t>
+          <t>1. E bấm "Từ chối" phiếu X, nhập lý do, xác nhận.</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Lý do từ chối: Nhắc trả hàng quá hạn trước</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>- Mở popup xem trước "Xem trước yêu cầu gia hạn hàng mượn &lt;mã&gt;" (không mở tab mới), khổ ngang.
-- Tiêu đề "PHIẾU YÊU CẦU GIA HẠN HÀNG MƯỢN", có mã phiếu và ngày lập, đầu trang là header công ty CỦA PHIẾU.
-- Thông tin: Người yêu cầu, Phòng ban, Phiếu mượn, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Ghi chú.
-- Bảng hàng 3 dòng + Tổng cộng; bảng cấp duyệt 3 dòng; 4 ô ký Người lập, Trưởng phòng, Ban giám đốc, Kế toán.</t>
+          <t>- Từ chối thành công, X thành Không duyệt.</t>
         </is>
       </c>
       <c r="J144" s="15" t="inlineStr"/>
@@ -9435,32 +9491,32 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>IN &amp; XUẤT EXCEL</t>
+          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
         </is>
       </c>
       <c r="C145" s="16" t="inlineStr">
         <is>
-          <t>TC_08.002</t>
+          <t>TC_07.005</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
         <is>
-          <t>In phiếu từ menu dòng ở danh sách</t>
+          <t>Super Admin không bị chặn</t>
         </is>
       </c>
       <c r="E145" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F145" s="15" t="inlineStr">
         <is>
-          <t>Có phiếu bất kỳ trong phạm vi.</t>
+          <t>Super Admin quản lý phòng P1 đang có nhân viên quá hạn.</t>
         </is>
       </c>
       <c r="G145" s="15" t="inlineStr">
         <is>
-          <t>1. Chọn Hành động &gt; In ở một dòng.</t>
+          <t>1. Super Admin duyệt phiếu Chờ TP duyệt của P1.</t>
         </is>
       </c>
       <c r="H145" s="15" t="inlineStr">
@@ -9470,7 +9526,7 @@
       </c>
       <c r="I145" s="15" t="inlineStr">
         <is>
-          <t>- Popup xem trước giống hệt khi in từ màn chi tiết.</t>
+          <t>- Duyệt thành công.</t>
         </is>
       </c>
       <c r="J145" s="15" t="inlineStr"/>
@@ -9494,7 +9550,7 @@
       <c r="P145" s="16" t="inlineStr"/>
       <c r="Q145" s="16" t="inlineStr"/>
     </row>
-    <row r="146" ht="34" customHeight="1">
+    <row r="146" ht="59" customHeight="1">
       <c r="A146" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9502,17 +9558,17 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>IN &amp; XUẤT EXCEL</t>
+          <t>CHẶN DUYỆT KHI CÒN HÀNG MƯỢN QUÁ HẠN</t>
         </is>
       </c>
       <c r="C146" s="16" t="inlineStr">
         <is>
-          <t>TC_08.003</t>
+          <t>TC_07.006</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>In phiếu bị từ chối</t>
+          <t>Kế toán / Ban giám đốc quản lý phòng có nhân viên quá hạn</t>
         </is>
       </c>
       <c r="E146" s="16" t="inlineStr">
@@ -9522,12 +9578,12 @@
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
-          <t>Phiếu bị Trưởng phòng từ chối.</t>
+          <t>Kế toán G (quyền Kế toán kho) đồng thời được phân công quản lý phòng P3; P3 có nhân viên mượn hàng quá hạn. Cấu hình chặn đang bật. Phiếu N Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>1. In phiếu.</t>
+          <t>1. G bấm "KT duyệt" phiếu N.</t>
         </is>
       </c>
       <c r="H146" s="15" t="inlineStr">
@@ -9537,8 +9593,8 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>- Bảng cấp duyệt ghi "Trưởng phòng (không duyệt)" kèm lý do.
-- Trạng thái ghi "Không duyệt".</t>
+          <t>- Phần mềm CŨNG chặn với cùng thông báo như TC_07.001.
+- Lưu ý: chốt chặn gắn trên thao tác duyệt nói chung, xét theo phòng ban NGƯỜI DUYỆT quản lý, không riêng cấp Trưởng phòng.</t>
         </is>
       </c>
       <c r="J146" s="15" t="inlineStr"/>
@@ -9562,121 +9618,76 @@
       <c r="P146" s="16" t="inlineStr"/>
       <c r="Q146" s="16" t="inlineStr"/>
     </row>
-    <row r="147" ht="34" customHeight="1">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="inlineStr">
+    <row r="147" ht="26" customHeight="1">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="13" t="n"/>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>VIII. IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n"/>
+      <c r="L147" s="4" t="n"/>
+      <c r="M147" s="4" t="n"/>
+      <c r="N147" s="4" t="n"/>
+      <c r="O147" s="4" t="n"/>
+      <c r="P147" s="4" t="n"/>
+      <c r="Q147" s="5" t="n"/>
+    </row>
+    <row r="148" ht="139" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
         <is>
           <t>IN &amp; XUẤT EXCEL</t>
         </is>
       </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.004</t>
-        </is>
-      </c>
-      <c r="D147" s="15" t="inlineStr">
-        <is>
-          <t>In phiếu chưa ai duyệt, ô rỗng để trống</t>
-        </is>
-      </c>
-      <c r="E147" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F147" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu vừa lập, không có ghi chú.</t>
-        </is>
-      </c>
-      <c r="G147" s="15" t="inlineStr">
-        <is>
-          <t>1. In phiếu.</t>
-        </is>
-      </c>
-      <c r="H147" s="15" t="inlineStr">
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.001</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>In một phiếu từ màn chi tiết</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu N Đã duyệt, qua đủ 3 cấp, phiếu mượn có 3 mặt hàng.</t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở chi tiết N, bấm "In".</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>- Không có bảng cấp duyệt.
-- Ô Ghi chú để TRỐNG, không in dấu gạch.</t>
-        </is>
-      </c>
-      <c r="J147" s="15" t="inlineStr"/>
-      <c r="K147" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L147" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M147" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N147" s="15" t="inlineStr"/>
-      <c r="O147" s="16" t="inlineStr"/>
-      <c r="P147" s="16" t="inlineStr"/>
-      <c r="Q147" s="16" t="inlineStr"/>
-    </row>
-    <row r="148" ht="124" customHeight="1">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="inlineStr">
-        <is>
-          <t>IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.005</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>In danh sách theo bộ lọc</t>
-        </is>
-      </c>
-      <c r="E148" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F148" s="15" t="inlineStr">
-        <is>
-          <t>Đã lọc Trạng thái = Đã duyệt, Ngày tạo 01/09/2026 - 30/09/2026, ra 25 phiếu (3 trang).</t>
-        </is>
-      </c>
-      <c r="G148" s="15" t="inlineStr">
-        <is>
-          <t>1. Bấm nút "In" trên thanh công cụ.</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="inlineStr">
-        <is>
-          <t>Trạng thái: Đã duyệt
-Ngày tạo: 01/09/2026 - 30/09/2026</t>
-        </is>
-      </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>- Popup "Xem trước danh sách yêu cầu gia hạn hàng mượn", khổ ngang.
-- Tiêu đề "DANH SÁCH PHIẾU YÊU CẦU GIA HẠN HÀNG MƯỢN"; "Khoảng thời gian: Từ ngày 01/09/2026 đến ngày 30/09/2026"; "Tổng số phiếu: 25".
-- In đủ 25 phiếu (không chỉ trang đang xem), cột: STT, Mã phiếu, Phiếu mượn, Người tạo, Ngày tạo, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Người duyệt, Ngày duyệt.</t>
+          <t>- Mở popup xem trước "Xem trước yêu cầu gia hạn hàng mượn &lt;mã&gt;" (không mở tab mới), khổ DỌC.
+- Tiêu đề "PHIẾU YÊU CẦU GIA HẠN HÀNG MƯỢN", có mã phiếu và ngày lập, đầu trang là header công ty CỦA PHIẾU.
+- Thông tin: Người yêu cầu, Phòng ban, Phiếu mượn, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Ghi chú.
+- Bảng hàng 3 dòng + Tổng cộng; bảng cấp duyệt 3 dòng; 4 ô ký Người lập, Trưởng phòng, Ban giám đốc, Kế toán.</t>
         </is>
       </c>
       <c r="J148" s="15" t="inlineStr"/>
@@ -9713,27 +9724,27 @@
       </c>
       <c r="C149" s="16" t="inlineStr">
         <is>
-          <t>TC_08.006</t>
+          <t>TC_08.002</t>
         </is>
       </c>
       <c r="D149" s="15" t="inlineStr">
         <is>
-          <t>In danh sách không có dữ liệu</t>
+          <t>In phiếu từ menu dòng ở danh sách</t>
         </is>
       </c>
       <c r="E149" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F149" s="15" t="inlineStr">
         <is>
-          <t>Bộ lọc không ra phiếu nào.</t>
+          <t>Có phiếu bất kỳ trong phạm vi.</t>
         </is>
       </c>
       <c r="G149" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm "In".</t>
+          <t>1. Chọn Hành động &gt; In ở một dòng.</t>
         </is>
       </c>
       <c r="H149" s="15" t="inlineStr">
@@ -9743,7 +9754,7 @@
       </c>
       <c r="I149" s="15" t="inlineStr">
         <is>
-          <t>- Bản in ghi "Không có dữ liệu", Tổng số phiếu: 0.</t>
+          <t>- Popup xem trước giống hệt khi in từ màn chi tiết.</t>
         </is>
       </c>
       <c r="J149" s="15" t="inlineStr"/>
@@ -9767,7 +9778,7 @@
       <c r="P149" s="16" t="inlineStr"/>
       <c r="Q149" s="16" t="inlineStr"/>
     </row>
-    <row r="150" ht="94" customHeight="1">
+    <row r="150" ht="34" customHeight="1">
       <c r="A150" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9780,27 +9791,27 @@
       </c>
       <c r="C150" s="16" t="inlineStr">
         <is>
-          <t>TC_08.007</t>
+          <t>TC_08.003</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Popup chọn trường xuất Excel tick sẵn cột đang hiện</t>
+          <t>In phiếu bị từ chối</t>
         </is>
       </c>
       <c r="E150" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>Cấu hình cột mặc định.</t>
+          <t>Phiếu bị Trưởng phòng từ chối.</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm "Xuất Excel".</t>
+          <t>1. In phiếu.</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
@@ -9810,8 +9821,8 @@
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>- Popup "Chọn trường xuất Excel" có 12 trường: Mã phiếu, Phiếu mượn, Người tạo, Ngày tạo, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Người duyệt, Ngày duyệt, Phòng ban, Ghi chú, Lý do từ chối.
-- Tick sẵn 9 trường đang hiện trên bảng; Phòng ban, Ghi chú, Lý do từ chối chưa tick.</t>
+          <t>- Bảng cấp duyệt ghi "Trưởng phòng (không duyệt)" kèm lý do.
+- Trạng thái ghi "Không duyệt".</t>
         </is>
       </c>
       <c r="J150" s="15" t="inlineStr"/>
@@ -9835,7 +9846,7 @@
       <c r="P150" s="16" t="inlineStr"/>
       <c r="Q150" s="16" t="inlineStr"/>
     </row>
-    <row r="151" ht="119" customHeight="1">
+    <row r="151" ht="34" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -9848,36 +9859,309 @@
       </c>
       <c r="C151" s="16" t="inlineStr">
         <is>
+          <t>TC_08.004</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>In phiếu chưa ai duyệt, ô rỗng để trống</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F151" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu vừa lập, không có ghi chú.</t>
+        </is>
+      </c>
+      <c r="G151" s="15" t="inlineStr">
+        <is>
+          <t>1. In phiếu.</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>- Không có bảng cấp duyệt.
+- Ô Ghi chú để TRỐNG, không in dấu gạch.</t>
+        </is>
+      </c>
+      <c r="J151" s="15" t="inlineStr"/>
+      <c r="K151" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L151" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M151" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N151" s="15" t="inlineStr"/>
+      <c r="O151" s="16" t="inlineStr"/>
+      <c r="P151" s="16" t="inlineStr"/>
+      <c r="Q151" s="16" t="inlineStr"/>
+    </row>
+    <row r="152" ht="124" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B152" s="15" t="inlineStr">
+        <is>
+          <t>IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.005</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>In danh sách theo bộ lọc</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F152" s="15" t="inlineStr">
+        <is>
+          <t>Đã lọc Trạng thái = Đã duyệt, Ngày tạo 01/09/2026 - 30/09/2026, ra 25 phiếu (3 trang).</t>
+        </is>
+      </c>
+      <c r="G152" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm nút "In" trên thanh công cụ.</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>Trạng thái: Đã duyệt
+Ngày tạo: 01/09/2026 - 30/09/2026</t>
+        </is>
+      </c>
+      <c r="I152" s="15" t="inlineStr">
+        <is>
+          <t>- Popup "Xem trước danh sách yêu cầu gia hạn hàng mượn", khổ ngang.
+- Tiêu đề "DANH SÁCH PHIẾU YÊU CẦU GIA HẠN HÀNG MƯỢN"; "Khoảng thời gian: Từ ngày 01/09/2026 đến ngày 30/09/2026"; "Tổng số phiếu: 25".
+- In đủ 25 phiếu (không chỉ trang đang xem), cột: STT, Mã phiếu, Phiếu mượn, Người tạo, Ngày tạo, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Người duyệt, Ngày duyệt.</t>
+        </is>
+      </c>
+      <c r="J152" s="15" t="inlineStr"/>
+      <c r="K152" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L152" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M152" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N152" s="15" t="inlineStr"/>
+      <c r="O152" s="16" t="inlineStr"/>
+      <c r="P152" s="16" t="inlineStr"/>
+      <c r="Q152" s="16" t="inlineStr"/>
+    </row>
+    <row r="153" ht="34" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="inlineStr">
+        <is>
+          <t>IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.006</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>In danh sách không có dữ liệu</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F153" s="15" t="inlineStr">
+        <is>
+          <t>Bộ lọc không ra phiếu nào.</t>
+        </is>
+      </c>
+      <c r="G153" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm "In".</t>
+        </is>
+      </c>
+      <c r="H153" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>- Bản in ghi "Không có dữ liệu", Tổng số phiếu: 0.</t>
+        </is>
+      </c>
+      <c r="J153" s="15" t="inlineStr"/>
+      <c r="K153" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L153" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M153" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N153" s="15" t="inlineStr"/>
+      <c r="O153" s="16" t="inlineStr"/>
+      <c r="P153" s="16" t="inlineStr"/>
+      <c r="Q153" s="16" t="inlineStr"/>
+    </row>
+    <row r="154" ht="94" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B154" s="15" t="inlineStr">
+        <is>
+          <t>IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.007</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>Popup chọn trường xuất Excel tick sẵn cột đang hiện</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F154" s="15" t="inlineStr">
+        <is>
+          <t>Cấu hình cột mặc định.</t>
+        </is>
+      </c>
+      <c r="G154" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm "Xuất Excel".</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I154" s="15" t="inlineStr">
+        <is>
+          <t>- Popup "Chọn trường xuất Excel" có 12 trường: Mã phiếu, Phiếu mượn, Người tạo, Ngày tạo, Ngày hẹn trả cũ, Ngày hẹn trả mới, Trạng thái, Người duyệt, Ngày duyệt, Phòng ban, Ghi chú, Lý do từ chối.
+- Tick sẵn 9 trường đang hiện trên bảng; Phòng ban, Ghi chú, Lý do từ chối chưa tick.</t>
+        </is>
+      </c>
+      <c r="J154" s="15" t="inlineStr"/>
+      <c r="K154" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L154" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M154" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N154" s="15" t="inlineStr"/>
+      <c r="O154" s="16" t="inlineStr"/>
+      <c r="P154" s="16" t="inlineStr"/>
+      <c r="Q154" s="16" t="inlineStr"/>
+    </row>
+    <row r="155" ht="119" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
           <t>TC_08.008</t>
         </is>
       </c>
-      <c r="D151" s="15" t="inlineStr">
+      <c r="D155" s="15" t="inlineStr">
         <is>
           <t>Nội dung file Excel</t>
         </is>
       </c>
-      <c r="E151" s="16" t="inlineStr">
+      <c r="E155" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F151" s="15" t="inlineStr">
+      <c r="F155" s="15" t="inlineStr">
         <is>
           <t>Đã lọc Ngày tạo 01/09/2026 - 30/09/2026, ra 25 phiếu.</t>
         </is>
       </c>
-      <c r="G151" s="15" t="inlineStr">
+      <c r="G155" s="15" t="inlineStr">
         <is>
           <t>1. Xuất Excel với các trường tick sẵn.
 2. Mở file.</t>
         </is>
       </c>
-      <c r="H151" s="15" t="inlineStr">
+      <c r="H155" s="15" t="inlineStr">
         <is>
           <t>Ngày tạo: 01/09/2026 - 30/09/2026</t>
         </is>
       </c>
-      <c r="I151" s="15" t="inlineStr">
+      <c r="I155" s="15" t="inlineStr">
         <is>
           <t>- Thông báo "Xuất Excel thành công"; tên file danh_sach_yeu_cau_gia_han_hang_muon.xlsx, sheet "Yêu cầu gia hạn hàng mượn".
 - Dòng 1 "DANH SÁCH PHIẾU YÊU CẦU GIA HẠN HÀNG MƯỢN"; dòng 2 "Từ ngày 01/09/2026 đến ngày 30/09/2026".
@@ -9885,277 +10169,6 @@
 - Cuối file có khối ký "Ngày…….Tháng…….Năm…….", "Người lập", "(Ký, họ tên)".</t>
         </is>
       </c>
-      <c r="J151" s="15" t="inlineStr"/>
-      <c r="K151" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L151" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M151" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N151" s="15" t="inlineStr"/>
-      <c r="O151" s="16" t="inlineStr"/>
-      <c r="P151" s="16" t="inlineStr"/>
-      <c r="Q151" s="16" t="inlineStr"/>
-    </row>
-    <row r="152" ht="34" customHeight="1">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B152" s="15" t="inlineStr">
-        <is>
-          <t>IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.009</t>
-        </is>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>Thứ tự cột Excel theo thứ tự tick</t>
-        </is>
-      </c>
-      <c r="E152" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F152" s="15" t="inlineStr">
-        <is>
-          <t>Mở popup xuất Excel.</t>
-        </is>
-      </c>
-      <c r="G152" s="15" t="inlineStr">
-        <is>
-          <t>1. Bỏ tick hết, tick lần lượt: Trạng thái, Mã phiếu, Lý do từ chối.
-2. Xuất và mở file.</t>
-        </is>
-      </c>
-      <c r="H152" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I152" s="15" t="inlineStr">
-        <is>
-          <t>- File có đúng 4 cột theo thứ tự: STT, Trạng thái, Mã phiếu, Lý do từ chối.</t>
-        </is>
-      </c>
-      <c r="J152" s="15" t="inlineStr"/>
-      <c r="K152" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L152" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M152" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N152" s="15" t="inlineStr"/>
-      <c r="O152" s="16" t="inlineStr"/>
-      <c r="P152" s="16" t="inlineStr"/>
-      <c r="Q152" s="16" t="inlineStr"/>
-    </row>
-    <row r="153" ht="34" customHeight="1">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="inlineStr">
-        <is>
-          <t>IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.010</t>
-        </is>
-      </c>
-      <c r="D153" s="15" t="inlineStr">
-        <is>
-          <t>Xuất Excel không lọc ngày thì không có dòng khoảng ngày</t>
-        </is>
-      </c>
-      <c r="E153" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F153" s="15" t="inlineStr">
-        <is>
-          <t>Không lọc Ngày tạo.</t>
-        </is>
-      </c>
-      <c r="G153" s="15" t="inlineStr">
-        <is>
-          <t>1. Xuất Excel, mở file.</t>
-        </is>
-      </c>
-      <c r="H153" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I153" s="15" t="inlineStr">
-        <is>
-          <t>- Dòng tiêu đề nằm ngay trên dòng tên cột, không có dòng "Từ ngày...".</t>
-        </is>
-      </c>
-      <c r="J153" s="15" t="inlineStr"/>
-      <c r="K153" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L153" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M153" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N153" s="15" t="inlineStr"/>
-      <c r="O153" s="16" t="inlineStr"/>
-      <c r="P153" s="16" t="inlineStr"/>
-      <c r="Q153" s="16" t="inlineStr"/>
-    </row>
-    <row r="154" ht="56" customHeight="1">
-      <c r="A154" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.011</t>
-        </is>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>Excel giữ đúng dạng mã và ngày</t>
-        </is>
-      </c>
-      <c r="E154" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F154" s="15" t="inlineStr">
-        <is>
-          <t>Xuất một file bất kỳ.</t>
-        </is>
-      </c>
-      <c r="G154" s="15" t="inlineStr">
-        <is>
-          <t>1. Mở file, bấm vào ô mã phiếu và ô ngày.</t>
-        </is>
-      </c>
-      <c r="H154" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I154" s="15" t="inlineStr">
-        <is>
-          <t>- Mã phiếu PGHHM-xxxxx không bị cảnh báo "số lưu dạng chữ".
-- Ngày hiện dd/mm/yyyy (hoặc dd/mm/yyyy hh:mm), không bị Excel đổi định dạng.
-- Ô không có dữ liệu để TRỐNG.</t>
-        </is>
-      </c>
-      <c r="J154" s="15" t="inlineStr"/>
-      <c r="K154" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L154" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M154" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N154" s="15" t="inlineStr"/>
-      <c r="O154" s="16" t="inlineStr"/>
-      <c r="P154" s="16" t="inlineStr"/>
-      <c r="Q154" s="16" t="inlineStr"/>
-    </row>
-    <row r="155" ht="34" customHeight="1">
-      <c r="A155" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t>IN &amp; XUẤT EXCEL</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>TC_08.012</t>
-        </is>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>Xuất Excel và In danh sách tuân phạm vi quyền</t>
-        </is>
-      </c>
-      <c r="E155" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F155" s="15" t="inlineStr">
-        <is>
-          <t>Tài khoản A không có quyền xem, lập 6 phiếu.</t>
-        </is>
-      </c>
-      <c r="G155" s="15" t="inlineStr">
-        <is>
-          <t>1. A xuất Excel và in danh sách, không lọc gì.</t>
-        </is>
-      </c>
-      <c r="H155" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>- Cả file Excel và bản in đều chỉ có 6 phiếu của A.</t>
-        </is>
-      </c>
       <c r="J155" s="15" t="inlineStr"/>
       <c r="K155" s="16" t="inlineStr">
         <is>
@@ -10190,12 +10203,12 @@
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
-          <t>TC_08.013</t>
+          <t>TC_08.009</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Xuất Excel ở lối vào "chờ duyệt"</t>
+          <t>Thứ tự cột Excel theo thứ tự tick</t>
         </is>
       </c>
       <c r="E156" s="16" t="inlineStr">
@@ -10205,12 +10218,13 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>Kế toán kho ở lối vào "chờ duyệt" đang thấy 3 phiếu.</t>
+          <t>Mở popup xuất Excel.</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>1. Xuất Excel.</t>
+          <t>1. Bỏ tick hết, tick lần lượt: Trạng thái, Mã phiếu, Lý do từ chối.
+2. Xuất và mở file.</t>
         </is>
       </c>
       <c r="H156" s="15" t="inlineStr">
@@ -10220,7 +10234,7 @@
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>- File có đúng 3 phiếu đang chờ Kế toán duyệt.</t>
+          <t>- File có đúng 4 cột theo thứ tự: STT, Trạng thái, Mã phiếu, Lý do từ chối.</t>
         </is>
       </c>
       <c r="J156" s="15" t="inlineStr"/>
@@ -10244,30 +10258,74 @@
       <c r="P156" s="16" t="inlineStr"/>
       <c r="Q156" s="16" t="inlineStr"/>
     </row>
-    <row r="157" ht="26" customHeight="1">
-      <c r="A157" s="13" t="n"/>
-      <c r="B157" s="13" t="n"/>
-      <c r="C157" s="14" t="inlineStr">
-        <is>
-          <t>IX. RÀNG BUỘC NHẬP LIỆU</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="n"/>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="4" t="n"/>
-      <c r="H157" s="4" t="n"/>
-      <c r="I157" s="4" t="n"/>
-      <c r="J157" s="4" t="n"/>
-      <c r="K157" s="4" t="n"/>
-      <c r="L157" s="4" t="n"/>
-      <c r="M157" s="4" t="n"/>
-      <c r="N157" s="4" t="n"/>
-      <c r="O157" s="4" t="n"/>
-      <c r="P157" s="4" t="n"/>
-      <c r="Q157" s="5" t="n"/>
-    </row>
-    <row r="158" ht="61" customHeight="1">
+    <row r="157" ht="34" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>IN &amp; XUẤT EXCEL</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>TC_08.010</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>Xuất Excel không lọc ngày thì không có dòng khoảng ngày</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F157" s="15" t="inlineStr">
+        <is>
+          <t>Không lọc Ngày tạo.</t>
+        </is>
+      </c>
+      <c r="G157" s="15" t="inlineStr">
+        <is>
+          <t>1. Xuất Excel, mở file.</t>
+        </is>
+      </c>
+      <c r="H157" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I157" s="15" t="inlineStr">
+        <is>
+          <t>- Dòng tiêu đề nằm ngay trên dòng tên cột, không có dòng "Từ ngày...".</t>
+        </is>
+      </c>
+      <c r="J157" s="15" t="inlineStr"/>
+      <c r="K157" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L157" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M157" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N157" s="15" t="inlineStr"/>
+      <c r="O157" s="16" t="inlineStr"/>
+      <c r="P157" s="16" t="inlineStr"/>
+      <c r="Q157" s="16" t="inlineStr"/>
+    </row>
+    <row r="158" ht="56" customHeight="1">
       <c r="A158" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -10275,32 +10333,32 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
+          <t>IN &amp; XUẤT EXCEL</t>
         </is>
       </c>
       <c r="C158" s="16" t="inlineStr">
         <is>
-          <t>TC_09.001</t>
+          <t>TC_08.011</t>
         </is>
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Gửi khi chưa chọn gì</t>
+          <t>Excel giữ đúng dạng mã và ngày</t>
         </is>
       </c>
       <c r="E158" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
-          <t>Đang ở màn Tạo mới, form trống.</t>
+          <t>Xuất một file bất kỳ.</t>
         </is>
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm "Gửi duyệt".</t>
+          <t>1. Mở file, bấm vào ô mã phiếu và ô ngày.</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
@@ -10310,9 +10368,9 @@
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>- Báo lỗi dưới ô phiếu "Phiếu yêu cầu xuất hàng mượn – Bắt buộc phải chọn".
-- Báo lỗi dưới ô ngày "Ngày hẹn trả mới – Bắt buộc phải chọn".
-- Màn cuộn tới lỗi đầu tiên; không sinh phiếu.</t>
+          <t>- Mã phiếu PGHHM-xxxxx không bị cảnh báo "số lưu dạng chữ".
+- Ngày hiện dd/mm/yyyy (hoặc dd/mm/yyyy hh:mm), không bị Excel đổi định dạng.
+- Ô không có dữ liệu để TRỐNG.</t>
         </is>
       </c>
       <c r="J158" s="15" t="inlineStr"/>
@@ -10344,32 +10402,32 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
+          <t>IN &amp; XUẤT EXCEL</t>
         </is>
       </c>
       <c r="C159" s="16" t="inlineStr">
         <is>
-          <t>TC_09.002</t>
+          <t>TC_08.012</t>
         </is>
       </c>
       <c r="D159" s="15" t="inlineStr">
         <is>
-          <t>Lỗi tự tắt khi đã chọn ngày</t>
+          <t>Xuất Excel và In danh sách tuân phạm vi quyền</t>
         </is>
       </c>
       <c r="E159" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F159" s="15" t="inlineStr">
         <is>
-          <t>Đang có lỗi đỏ ở ô Ngày hẹn trả mới.</t>
+          <t>Tài khoản A không có quyền xem, lập 6 phiếu.</t>
         </is>
       </c>
       <c r="G159" s="15" t="inlineStr">
         <is>
-          <t>1. Chọn một ngày hợp lệ.</t>
+          <t>1. A xuất Excel và in danh sách, không lọc gì.</t>
         </is>
       </c>
       <c r="H159" s="15" t="inlineStr">
@@ -10379,7 +10437,7 @@
       </c>
       <c r="I159" s="15" t="inlineStr">
         <is>
-          <t>- Viền đỏ và dòng lỗi dưới ô biến mất ngay, không cần bấm Gửi lại.</t>
+          <t>- Cả file Excel và bản in đều chỉ có 6 phiếu của A.</t>
         </is>
       </c>
       <c r="J159" s="15" t="inlineStr"/>
@@ -10411,17 +10469,17 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
+          <t>IN &amp; XUẤT EXCEL</t>
         </is>
       </c>
       <c r="C160" s="16" t="inlineStr">
         <is>
-          <t>TC_09.003</t>
+          <t>TC_08.013</t>
         </is>
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>Ghi chú tối đa 255 ký tự</t>
+          <t>Xuất Excel ở lối vào "chờ duyệt"</t>
         </is>
       </c>
       <c r="E160" s="16" t="inlineStr">
@@ -10431,22 +10489,22 @@
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>Đang ở màn Tạo mới.</t>
+          <t>Kế toán kho ở lối vào "chờ duyệt" đang thấy 3 phiếu.</t>
         </is>
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>1. Dán đoạn văn 300 ký tự vào ô Ghi chú.</t>
+          <t>1. Xuất Excel.</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Ghi chú: 300 ký tự</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>- Ô chỉ nhận 255 ký tự đầu.</t>
+          <t>- File có đúng 3 phiếu đang chờ Kế toán duyệt.</t>
         </is>
       </c>
       <c r="J160" s="15" t="inlineStr"/>
@@ -10470,92 +10528,48 @@
       <c r="P160" s="16" t="inlineStr"/>
       <c r="Q160" s="16" t="inlineStr"/>
     </row>
-    <row r="161" ht="34" customHeight="1">
-      <c r="A161" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B161" s="15" t="inlineStr">
+    <row r="161" ht="26" customHeight="1">
+      <c r="A161" s="13" t="n"/>
+      <c r="B161" s="13" t="n"/>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>IX. RÀNG BUỘC NHẬP LIỆU</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
+      <c r="P161" s="4" t="n"/>
+      <c r="Q161" s="5" t="n"/>
+    </row>
+    <row r="162" ht="82" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
         <is>
           <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>TC_09.004</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối tối đa 255 ký tự</t>
-        </is>
-      </c>
-      <c r="E161" s="16" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F161" s="15" t="inlineStr">
-        <is>
-          <t>Đang mở popup Từ chối.</t>
-        </is>
-      </c>
-      <c r="G161" s="15" t="inlineStr">
-        <is>
-          <t>1. Dán đoạn 300 ký tự vào ô lý do.</t>
-        </is>
-      </c>
-      <c r="H161" s="15" t="inlineStr">
-        <is>
-          <t>Lý do: 300 ký tự</t>
-        </is>
-      </c>
-      <c r="I161" s="15" t="inlineStr">
-        <is>
-          <t>- Ô chỉ nhận 255 ký tự.</t>
-        </is>
-      </c>
-      <c r="J161" s="15" t="inlineStr"/>
-      <c r="K161" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L161" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M161" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N161" s="15" t="inlineStr"/>
-      <c r="O161" s="16" t="inlineStr"/>
-      <c r="P161" s="16" t="inlineStr"/>
-      <c r="Q161" s="16" t="inlineStr"/>
-    </row>
-    <row r="162" ht="34" customHeight="1">
-      <c r="A162" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B162" s="15" t="inlineStr">
-        <is>
-          <t>RÀNG BUỘC NHẬP LIỆU</t>
-        </is>
-      </c>
       <c r="C162" s="16" t="inlineStr">
         <is>
-          <t>TC_09.005</t>
+          <t>TC_09.001</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Chỉ nhận file PDF</t>
+          <t>Gửi khi chưa chọn gì</t>
         </is>
       </c>
       <c r="E162" s="16" t="inlineStr">
@@ -10565,24 +10579,25 @@
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
-          <t>Đang ở màn Tạo mới.</t>
+          <t>Đang ở màn Tạo mới, form trống.</t>
         </is>
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>1. Tải lên file bao_gia.docx.
-2. Tải lên file anh.jpg.</t>
+          <t>1. Bấm "Gửi duyệt".</t>
         </is>
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>File: bao_gia.docx
-File: anh.jpg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>- Cả hai đều bị từ chối, báo chỉ nhận file PDF; không có file nào được thêm.</t>
+          <t>- Báo lỗi dưới ô phiếu "Phiếu yêu cầu xuất hàng mượn – Bắt buộc phải chọn".
+- Báo lỗi dưới ô ngày "Ngày hẹn trả mới – Bắt buộc phải chọn".
+- Kèm thông báo góc màn hình "Bạn chưa nhập đầy đủ thông tin."
+- Màn cuộn tới lỗi đầu tiên; không sinh phiếu.</t>
         </is>
       </c>
       <c r="J162" s="15" t="inlineStr"/>
@@ -10619,12 +10634,12 @@
       </c>
       <c r="C163" s="16" t="inlineStr">
         <is>
-          <t>TC_09.006</t>
+          <t>TC_09.002</t>
         </is>
       </c>
       <c r="D163" s="15" t="inlineStr">
         <is>
-          <t>File vượt 13 MB</t>
+          <t>Lỗi tự tắt khi đã chọn ngày</t>
         </is>
       </c>
       <c r="E163" s="16" t="inlineStr">
@@ -10634,22 +10649,22 @@
       </c>
       <c r="F163" s="15" t="inlineStr">
         <is>
-          <t>Có file PDF 15 MB.</t>
+          <t>Đang có lỗi đỏ ở ô Ngày hẹn trả mới.</t>
         </is>
       </c>
       <c r="G163" s="15" t="inlineStr">
         <is>
-          <t>1. Tải lên file 15 MB.</t>
+          <t>1. Chọn một ngày hợp lệ.</t>
         </is>
       </c>
       <c r="H163" s="15" t="inlineStr">
         <is>
-          <t>File: tai_lieu_15MB.pdf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I163" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, báo file không được quá 13 MB.</t>
+          <t>- Viền đỏ và dòng lỗi dưới ô biến mất ngay, không cần bấm Gửi lại.</t>
         </is>
       </c>
       <c r="J163" s="15" t="inlineStr"/>
@@ -10686,12 +10701,12 @@
       </c>
       <c r="C164" s="16" t="inlineStr">
         <is>
-          <t>TC_09.007</t>
+          <t>TC_09.003</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Gọi thẳng chức năng lập phiếu với ngày hôm nay</t>
+          <t>Ghi chú tối đa 255 ký tự</t>
         </is>
       </c>
       <c r="E164" s="16" t="inlineStr">
@@ -10701,22 +10716,22 @@
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>Hôm nay 30/09/2026; phiếu mượn đủ điều kiện, hạn 23/09.</t>
+          <t>Đang ở màn Tạo mới.</t>
         </is>
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 30/09/2026.</t>
+          <t>1. Dán đoạn văn 300 ký tự vào ô Ghi chú.</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>Ngày hẹn trả mới: 30/09/2026</t>
+          <t>Ghi chú: 300 ký tự</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, lỗi ô Ngày hẹn trả mới "Phải sau ngày hôm nay"; không sinh phiếu.</t>
+          <t>- Ô chỉ nhận 255 ký tự đầu.</t>
         </is>
       </c>
       <c r="J164" s="15" t="inlineStr"/>
@@ -10753,37 +10768,37 @@
       </c>
       <c r="C165" s="16" t="inlineStr">
         <is>
-          <t>TC_09.008</t>
+          <t>TC_09.004</t>
         </is>
       </c>
       <c r="D165" s="15" t="inlineStr">
         <is>
-          <t>Gọi thẳng chức năng lập phiếu với ngày vượt trần</t>
+          <t>Lý do từ chối tối đa 255 ký tự</t>
         </is>
       </c>
       <c r="E165" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F165" s="15" t="inlineStr">
         <is>
-          <t>Hôm nay 30/09/2026, ngày trần 07/10/2026.</t>
+          <t>Đang mở popup Từ chối.</t>
         </is>
       </c>
       <c r="G165" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 10/10/2026.</t>
+          <t>1. Dán đoạn 300 ký tự vào ô lý do.</t>
         </is>
       </c>
       <c r="H165" s="15" t="inlineStr">
         <is>
-          <t>Ngày hẹn trả mới: 10/10/2026</t>
+          <t>Lý do: 300 ký tự</t>
         </is>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, báo "Không thể mượn quá 07/10/2026"; không sinh phiếu.</t>
+          <t>- Ô chỉ nhận 255 ký tự.</t>
         </is>
       </c>
       <c r="J165" s="15" t="inlineStr"/>
@@ -10820,12 +10835,12 @@
       </c>
       <c r="C166" s="16" t="inlineStr">
         <is>
-          <t>TC_09.009</t>
+          <t>TC_09.005</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>Gọi thẳng chức năng lập phiếu với ngày không sau hạn trả hiện tại</t>
+          <t>Chỉ nhận file PDF</t>
         </is>
       </c>
       <c r="E166" s="16" t="inlineStr">
@@ -10835,22 +10850,24 @@
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn hạn trả 03/10/2026.</t>
+          <t>Đang ở màn Tạo mới.</t>
         </is>
       </c>
       <c r="G166" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 03/10/2026.</t>
+          <t>1. Tải lên file bao_gia.docx.
+2. Tải lên file anh.jpg.</t>
         </is>
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>Ngày hẹn trả mới: 03/10/2026</t>
+          <t>File: bao_gia.docx
+File: anh.jpg</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, báo "Phải sau ngày hẹn trả hiện tại (03/10/2026)"; không sinh phiếu.</t>
+          <t>- Cả hai đều bị từ chối, báo chỉ nhận file PDF; không có file nào được thêm.</t>
         </is>
       </c>
       <c r="J166" s="15" t="inlineStr"/>
@@ -10887,37 +10904,37 @@
       </c>
       <c r="C167" s="16" t="inlineStr">
         <is>
-          <t>TC_09.010</t>
+          <t>TC_09.006</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
         <is>
-          <t>Gọi thẳng chức năng lập phiếu cho phiếu mượn của người khác</t>
+          <t>File vượt 13 MB</t>
         </is>
       </c>
       <c r="E167" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F167" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn M thuộc nhân viên B; đăng nhập bằng A.</t>
+          <t>Có file PDF 15 MB.</t>
         </is>
       </c>
       <c r="G167" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu gia hạn cho M.</t>
+          <t>1. Tải lên file 15 MB.</t>
         </is>
       </c>
       <c r="H167" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>File: tai_lieu_15MB.pdf</t>
         </is>
       </c>
       <c r="I167" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, lỗi "Không thể gia hạn yêu cầu này!"; không sinh phiếu.</t>
+          <t>- Bị từ chối, báo file không được quá 13 MB.</t>
         </is>
       </c>
       <c r="J167" s="15" t="inlineStr"/>
@@ -10941,7 +10958,7 @@
       <c r="P167" s="16" t="inlineStr"/>
       <c r="Q167" s="16" t="inlineStr"/>
     </row>
-    <row r="168" ht="41" customHeight="1">
+    <row r="168" ht="34" customHeight="1">
       <c r="A168" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -10954,37 +10971,37 @@
       </c>
       <c r="C168" s="16" t="inlineStr">
         <is>
-          <t>TC_09.011</t>
+          <t>TC_09.007</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>Gọi thẳng chức năng lấy dữ liệu phiếu mượn không đủ điều kiện</t>
+          <t>Gọi thẳng chức năng lập phiếu với ngày hôm nay</t>
         </is>
       </c>
       <c r="E168" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>Phiếu mượn M đang có yêu cầu gia hạn chờ duyệt.</t>
+          <t>Hôm nay 30/09/2026; phiếu mượn đủ điều kiện, hạn 23/09.</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>1. Dùng công cụ kiểm thử gọi chức năng lấy dữ liệu phiếu mượn M để lập phiếu.</t>
+          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 30/09/2026.</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ngày hẹn trả mới: 30/09/2026</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>- Báo "Phiếu mượn này không gia hạn được: không phải phiếu của bạn, đã trả hết hàng, hoặc đang có yêu cầu gia hạn chờ duyệt."</t>
+          <t>- Bị từ chối, lỗi ô Ngày hẹn trả mới "Phải sau ngày hôm nay"; không sinh phiếu.</t>
         </is>
       </c>
       <c r="J168" s="15" t="inlineStr"/>
@@ -11021,37 +11038,37 @@
       </c>
       <c r="C169" s="16" t="inlineStr">
         <is>
-          <t>TC_09.012</t>
+          <t>TC_09.008</t>
         </is>
       </c>
       <c r="D169" s="15" t="inlineStr">
         <is>
-          <t>Ngày gõ tay sai định dạng</t>
+          <t>Gọi thẳng chức năng lập phiếu với ngày vượt trần</t>
         </is>
       </c>
       <c r="E169" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F169" s="15" t="inlineStr">
         <is>
-          <t>Dùng công cụ kiểm thử.</t>
+          <t>Hôm nay 30/09/2026, ngày trần 07/10/2026.</t>
         </is>
       </c>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>1. Gửi lệnh lập phiếu với Ngày hẹn trả mới "31/02/2026".</t>
+          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 10/10/2026.</t>
         </is>
       </c>
       <c r="H169" s="15" t="inlineStr">
         <is>
-          <t>Ngày hẹn trả mới: 31/02/2026</t>
+          <t>Ngày hẹn trả mới: 10/10/2026</t>
         </is>
       </c>
       <c r="I169" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối, lỗi ô Ngày hẹn trả mới "Không hợp lệ".</t>
+          <t>- Bị từ chối, báo "Không thể mượn quá 07/10/2026"; không sinh phiếu.</t>
         </is>
       </c>
       <c r="J169" s="15" t="inlineStr"/>
@@ -11075,30 +11092,74 @@
       <c r="P169" s="16" t="inlineStr"/>
       <c r="Q169" s="16" t="inlineStr"/>
     </row>
-    <row r="170" ht="26" customHeight="1">
-      <c r="A170" s="13" t="n"/>
-      <c r="B170" s="13" t="n"/>
-      <c r="C170" s="14" t="inlineStr">
-        <is>
-          <t>X. CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="n"/>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="4" t="n"/>
-      <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="n"/>
-      <c r="I170" s="4" t="n"/>
-      <c r="J170" s="4" t="n"/>
-      <c r="K170" s="4" t="n"/>
-      <c r="L170" s="4" t="n"/>
-      <c r="M170" s="4" t="n"/>
-      <c r="N170" s="4" t="n"/>
-      <c r="O170" s="4" t="n"/>
-      <c r="P170" s="4" t="n"/>
-      <c r="Q170" s="5" t="n"/>
-    </row>
-    <row r="171" ht="35" customHeight="1">
+    <row r="170" ht="34" customHeight="1">
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B170" s="15" t="inlineStr">
+        <is>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>TC_09.009</t>
+        </is>
+      </c>
+      <c r="D170" s="15" t="inlineStr">
+        <is>
+          <t>Gọi thẳng chức năng lập phiếu với ngày không sau hạn trả hiện tại</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F170" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu mượn hạn trả 03/10/2026.</t>
+        </is>
+      </c>
+      <c r="G170" s="15" t="inlineStr">
+        <is>
+          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu với Ngày hẹn trả mới 03/10/2026.</t>
+        </is>
+      </c>
+      <c r="H170" s="15" t="inlineStr">
+        <is>
+          <t>Ngày hẹn trả mới: 03/10/2026</t>
+        </is>
+      </c>
+      <c r="I170" s="15" t="inlineStr">
+        <is>
+          <t>- Bị từ chối, báo "Phải sau ngày hẹn trả hiện tại (03/10/2026)"; không sinh phiếu.</t>
+        </is>
+      </c>
+      <c r="J170" s="15" t="inlineStr"/>
+      <c r="K170" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L170" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M170" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N170" s="15" t="inlineStr"/>
+      <c r="O170" s="16" t="inlineStr"/>
+      <c r="P170" s="16" t="inlineStr"/>
+      <c r="Q170" s="16" t="inlineStr"/>
+    </row>
+    <row r="171" ht="39" customHeight="1">
       <c r="A171" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11106,17 +11167,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
       <c r="C171" s="16" t="inlineStr">
         <is>
-          <t>TC_10.001</t>
+          <t>TC_09.010</t>
         </is>
       </c>
       <c r="D171" s="15" t="inlineStr">
         <is>
-          <t>Lập phiếu thứ hai khi phiếu đầu còn chờ duyệt</t>
+          <t>Gọi thẳng chức năng lập phiếu cho phiếu mượn của người khác</t>
         </is>
       </c>
       <c r="E171" s="16" t="inlineStr">
@@ -11126,13 +11187,12 @@
       </c>
       <c r="F171" s="15" t="inlineStr">
         <is>
-          <t>A mở màn Tạo mới ở 2 tab, cả hai đều đã chọn cùng phiếu mượn M.</t>
+          <t>Phiếu mượn M (mã PYCXH-35542) thuộc nhân viên B; đăng nhập bằng A.</t>
         </is>
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>1. Tab 1 bấm "Gửi duyệt" (thành công).
-2. Tab 2 bấm "Gửi duyệt".</t>
+          <t>1. Dùng công cụ kiểm thử gửi lệnh lập phiếu gia hạn cho M.</t>
         </is>
       </c>
       <c r="H171" s="15" t="inlineStr">
@@ -11142,8 +11202,7 @@
       </c>
       <c r="I171" s="15" t="inlineStr">
         <is>
-          <t>- Tab 2 báo lỗi dưới ô phiếu "Không thể gia hạn yêu cầu này!".
-- M chỉ có MỘT phiếu gia hạn đang chờ duyệt.</t>
+          <t>- Bị từ chối, lỗi "Không thể gia hạn yêu cầu này: chỉ người lập phiếu PYCXH-35542 mới được gia hạn."; không sinh phiếu.</t>
         </is>
       </c>
       <c r="J171" s="15" t="inlineStr"/>
@@ -11167,7 +11226,7 @@
       <c r="P171" s="16" t="inlineStr"/>
       <c r="Q171" s="16" t="inlineStr"/>
     </row>
-    <row r="172" ht="41" customHeight="1">
+    <row r="172" ht="94" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11175,33 +11234,32 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
         <is>
-          <t>TC_10.002</t>
+          <t>TC_09.011</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>Hai Trưởng phòng cùng duyệt một phiếu</t>
+          <t>Gọi thẳng chức năng lấy dữ liệu phiếu mượn không đủ điều kiện</t>
         </is>
       </c>
       <c r="E172" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
-          <t>E và E3 cùng quản lý P1, cùng mở phiếu X Chờ TP duyệt.</t>
+          <t>Phiếu mượn M (mã PYCXH-35542) của A đang có yêu cầu gia hạn PGHHM-02950 Chờ TP duyệt.</t>
         </is>
       </c>
       <c r="G172" s="15" t="inlineStr">
         <is>
-          <t>1. E bấm TP duyệt (thành công).
-2. E3 bấm TP duyệt ngay sau.</t>
+          <t>1. Đăng nhập A, dùng công cụ kiểm thử gọi chức năng lấy dữ liệu phiếu mượn M để lập phiếu.</t>
         </is>
       </c>
       <c r="H172" s="15" t="inlineStr">
@@ -11211,8 +11269,8 @@
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>- E3 bị từ chối (phiếu đã sang cấp khác), báo không có quyền duyệt bước này.
-- Lịch sử chỉ có MỘT dòng "Trưởng phòng duyệt".</t>
+          <t>- Báo "Không thể gia hạn yêu cầu này: phiếu PYCXH-35542 đang có yêu cầu gia hạn PGHHM-02950 (Chờ TP duyệt) chưa duyệt xong. Chờ yêu cầu đó được duyệt hoặc từ chối rồi mới lập yêu cầu mới."
+- Lưu ý: câu báo nêu đúng LÝ DO đầu tiên gặp phải (Redmine #11529), không còn câu chung chung.</t>
         </is>
       </c>
       <c r="J172" s="15" t="inlineStr"/>
@@ -11236,7 +11294,7 @@
       <c r="P172" s="16" t="inlineStr"/>
       <c r="Q172" s="16" t="inlineStr"/>
     </row>
-    <row r="173" ht="38" customHeight="1">
+    <row r="173" ht="34" customHeight="1">
       <c r="A173" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11244,44 +11302,42 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+          <t>RÀNG BUỘC NHẬP LIỆU</t>
         </is>
       </c>
       <c r="C173" s="16" t="inlineStr">
         <is>
-          <t>TC_10.003</t>
+          <t>TC_09.012</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
         <is>
-          <t>Một người duyệt, người khác từ chối cùng lúc</t>
+          <t>Ngày gõ tay sai định dạng</t>
         </is>
       </c>
       <c r="E173" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F173" s="15" t="inlineStr">
         <is>
-          <t>Hai Kế toán kho G và G2 cùng mở phiếu N Chờ KT duyệt.</t>
+          <t>Dùng công cụ kiểm thử.</t>
         </is>
       </c>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>1. G bấm KT duyệt (thành công).
-2. G2 mở popup Từ chối, nhập lý do, xác nhận.</t>
+          <t>1. Gửi lệnh lập phiếu với Ngày hẹn trả mới "31/02/2026".</t>
         </is>
       </c>
       <c r="H173" s="15" t="inlineStr">
         <is>
-          <t>Lý do từ chối: Test đồng thời</t>
+          <t>Ngày hẹn trả mới: 31/02/2026</t>
         </is>
       </c>
       <c r="I173" s="15" t="inlineStr">
         <is>
-          <t>- G2 bị từ chối, popup hiện lỗi "Bạn không có quyền từ chối phiếu này."
-- N vẫn Đã duyệt; phiếu mượn giữ ngày mới.</t>
+          <t>- Bị từ chối, lỗi ô Ngày hẹn trả mới "Không hợp lệ".</t>
         </is>
       </c>
       <c r="J173" s="15" t="inlineStr"/>
@@ -11305,118 +11361,75 @@
       <c r="P173" s="16" t="inlineStr"/>
       <c r="Q173" s="16" t="inlineStr"/>
     </row>
-    <row r="174" ht="34" customHeight="1">
-      <c r="A174" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B174" s="15" t="inlineStr">
+    <row r="174" ht="26" customHeight="1">
+      <c r="A174" s="13" t="n"/>
+      <c r="B174" s="13" t="n"/>
+      <c r="C174" s="14" t="inlineStr">
+        <is>
+          <t>X. CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="4" t="n"/>
+      <c r="H174" s="4" t="n"/>
+      <c r="I174" s="4" t="n"/>
+      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
+      <c r="Q174" s="5" t="n"/>
+    </row>
+    <row r="175" ht="95" customHeight="1">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B175" s="15" t="inlineStr">
         <is>
           <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
         </is>
       </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>TC_10.004</t>
-        </is>
-      </c>
-      <c r="D174" s="15" t="inlineStr">
-        <is>
-          <t>Người duyệt ở công ty khác không thấy phiếu</t>
-        </is>
-      </c>
-      <c r="E174" s="16" t="inlineStr">
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t>TC_10.001</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="inlineStr">
+        <is>
+          <t>Lập phiếu thứ hai khi phiếu đầu còn chờ duyệt</t>
+        </is>
+      </c>
+      <c r="E175" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F174" s="15" t="inlineStr">
-        <is>
-          <t>Kế toán kho H thuộc công ty 4; công ty 1 có 3 phiếu Chờ KT duyệt.</t>
-        </is>
-      </c>
-      <c r="G174" s="15" t="inlineStr">
-        <is>
-          <t>1. H mở lối vào "chờ duyệt".</t>
-        </is>
-      </c>
-      <c r="H174" s="15" t="inlineStr">
+      <c r="F175" s="15" t="inlineStr">
+        <is>
+          <t>A mở màn Tạo mới ở 2 tab, cả hai đều đã chọn cùng phiếu mượn M.</t>
+        </is>
+      </c>
+      <c r="G175" s="15" t="inlineStr">
+        <is>
+          <t>1. Tab 1 bấm "Gửi duyệt" (thành công).
+2. Tab 2 bấm "Gửi duyệt".</t>
+        </is>
+      </c>
+      <c r="H175" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I174" s="15" t="inlineStr">
-        <is>
-          <t>- Danh sách không có 3 phiếu của công ty 1.</t>
-        </is>
-      </c>
-      <c r="J174" s="15" t="inlineStr"/>
-      <c r="K174" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L174" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M174" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N174" s="15" t="inlineStr"/>
-      <c r="O174" s="16" t="inlineStr"/>
-      <c r="P174" s="16" t="inlineStr"/>
-      <c r="Q174" s="16" t="inlineStr"/>
-    </row>
-    <row r="175" ht="36" customHeight="1">
-      <c r="A175" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B175" s="15" t="inlineStr">
-        <is>
-          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
-        </is>
-      </c>
-      <c r="C175" s="16" t="inlineStr">
-        <is>
-          <t>TC_10.005</t>
-        </is>
-      </c>
-      <c r="D175" s="15" t="inlineStr">
-        <is>
-          <t>Trưởng phòng công ty khác trùng phòng ban không duyệt được</t>
-        </is>
-      </c>
-      <c r="E175" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F175" s="15" t="inlineStr">
-        <is>
-          <t>Trưởng phòng E4 thuộc công ty 4 nhưng được gán quản lý một phòng ban trùng với phòng của phiếu X (công ty 1).</t>
-        </is>
-      </c>
-      <c r="G175" s="15" t="inlineStr">
-        <is>
-          <t>1. Dùng công cụ kiểm thử gọi chức năng duyệt X bằng E4.</t>
-        </is>
-      </c>
-      <c r="H175" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I175" s="15" t="inlineStr">
         <is>
-          <t>- Bị từ chối "Bạn không có quyền duyệt bước này."
-- Lưu ý: ERP cho qua trường hợp này; hệ thống mới đã chặn.</t>
+          <t>- Tab 2 báo lỗi dưới ô phiếu (kèm thông báo góc màn hình) "Không thể gia hạn yêu cầu này: phiếu &lt;mã M&gt; đang có yêu cầu gia hạn &lt;mã phiếu tab 1&gt; (Chờ TP duyệt) chưa duyệt xong. Chờ yêu cầu đó được duyệt hoặc từ chối rồi mới lập yêu cầu mới."
+- M chỉ có MỘT phiếu gia hạn đang chờ duyệt.</t>
         </is>
       </c>
       <c r="J175" s="15" t="inlineStr"/>
@@ -11440,7 +11453,7 @@
       <c r="P175" s="16" t="inlineStr"/>
       <c r="Q175" s="16" t="inlineStr"/>
     </row>
-    <row r="176" ht="35" customHeight="1">
+    <row r="176" ht="41" customHeight="1">
       <c r="A176" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11453,40 +11466,39 @@
       </c>
       <c r="C176" s="16" t="inlineStr">
         <is>
-          <t>TC_10.006</t>
+          <t>TC_10.002</t>
         </is>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>Bộ lọc không làm lộ phiếu ngoài phạm vi ở lối "chờ duyệt"</t>
+          <t>Hai Trưởng phòng cùng duyệt một phiếu</t>
         </is>
       </c>
       <c r="E176" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
-          <t>Trưởng phòng E (có thêm Kế toán kho để thấy menu) quản lý P1. P2 có phiếu Chờ TP duyệt do nhân viên X lập.</t>
+          <t>E và E3 cùng quản lý P1, cùng mở phiếu X Chờ TP duyệt.</t>
         </is>
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>1. E mở lối vào "chờ duyệt".
-2. Lọc Người tạo = X.
-3. Lọc Trạng thái = Chờ TP duyệt.</t>
+          <t>1. E bấm TP duyệt (thành công).
+2. E3 bấm TP duyệt ngay sau.</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>Người tạo: X
-Trạng thái: Chờ TP duyệt</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>- Không ra phiếu nào của P2.</t>
+          <t>- E3 bị từ chối (phiếu đã sang cấp khác), báo không có quyền duyệt bước này.
+- Lịch sử chỉ có MỘT dòng "Trưởng phòng duyệt".</t>
         </is>
       </c>
       <c r="J176" s="15" t="inlineStr"/>
@@ -11510,7 +11522,7 @@
       <c r="P176" s="16" t="inlineStr"/>
       <c r="Q176" s="16" t="inlineStr"/>
     </row>
-    <row r="177" ht="52" customHeight="1">
+    <row r="177" ht="38" customHeight="1">
       <c r="A177" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11523,40 +11535,39 @@
       </c>
       <c r="C177" s="16" t="inlineStr">
         <is>
-          <t>TC_10.007</t>
+          <t>TC_10.003</t>
         </is>
       </c>
       <c r="D177" s="15" t="inlineStr">
         <is>
-          <t>Phiếu Không duyệt hiện theo phạm vi quyền</t>
+          <t>Một người duyệt, người khác từ chối cùng lúc</t>
         </is>
       </c>
       <c r="E177" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F177" s="15" t="inlineStr">
         <is>
-          <t>Phiếu X do B lập, bị Trưởng phòng E từ chối. C có quyền Xem theo công ty.</t>
+          <t>Hai Kế toán kho G và G2 cùng mở phiếu N Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G177" s="15" t="inlineStr">
         <is>
-          <t>1. C lọc Trạng thái = Không duyệt.
-2. E (chỉ có quyền Trưởng phòng duyệt) mở danh sách.</t>
+          <t>1. G bấm KT duyệt (thành công).
+2. G2 mở popup Từ chối, nhập lý do, xác nhận.</t>
         </is>
       </c>
       <c r="H177" s="15" t="inlineStr">
         <is>
-          <t>Trạng thái: Không duyệt</t>
+          <t>Lý do từ chối: Test đồng thời</t>
         </is>
       </c>
       <c r="I177" s="15" t="inlineStr">
         <is>
-          <t>- C thấy X.
-- E vẫn thấy X (người đã từ chối), bấm vào mở được.
-- Lưu ý: ERP giấu phiếu Không duyệt với mọi người trừ người lập; hệ thống mới đã bỏ luật này.</t>
+          <t>- G2 bị từ chối, popup hiện lỗi "Bạn không có quyền từ chối phiếu này."
+- N vẫn Đã duyệt; phiếu mượn giữ ngày mới.</t>
         </is>
       </c>
       <c r="J177" s="15" t="inlineStr"/>
@@ -11580,7 +11591,7 @@
       <c r="P177" s="16" t="inlineStr"/>
       <c r="Q177" s="16" t="inlineStr"/>
     </row>
-    <row r="178" ht="55" customHeight="1">
+    <row r="178" ht="34" customHeight="1">
       <c r="A178" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11593,27 +11604,27 @@
       </c>
       <c r="C178" s="16" t="inlineStr">
         <is>
-          <t>TC_10.008</t>
+          <t>TC_10.004</t>
         </is>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>Quyền tổng công ty mở phiếu công ty khác bằng đường dẫn</t>
+          <t>Người duyệt ở công ty khác không thấy phiếu</t>
         </is>
       </c>
       <c r="E178" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
         <is>
-          <t>B có quyền Xem theo tổng công ty (công ty 1). Phiếu W thuộc công ty 4.</t>
+          <t>Kế toán kho H thuộc công ty 4; công ty 1 có 3 phiếu Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>1. B dán đường dẫn chi tiết phiếu W.</t>
+          <t>1. H mở lối vào "chờ duyệt".</t>
         </is>
       </c>
       <c r="H178" s="15" t="inlineStr">
@@ -11623,8 +11634,7 @@
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>- Mở xem được nội dung W (chỉ xem, không có nút duyệt).
-- Ghi nhận: danh sách của B KHÔNG liệt kê W; hai nơi lệch nhau, báo lại cho nhóm phát triển nếu cần thống nhất.</t>
+          <t>- Danh sách không có 3 phiếu của công ty 1.</t>
         </is>
       </c>
       <c r="J178" s="15" t="inlineStr"/>
@@ -11648,30 +11658,75 @@
       <c r="P178" s="16" t="inlineStr"/>
       <c r="Q178" s="16" t="inlineStr"/>
     </row>
-    <row r="179" ht="26" customHeight="1">
-      <c r="A179" s="13" t="n"/>
-      <c r="B179" s="13" t="n"/>
-      <c r="C179" s="14" t="inlineStr">
-        <is>
-          <t>XI. LỊCH SỬ THAY ĐỔI</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="n"/>
-      <c r="E179" s="4" t="n"/>
-      <c r="F179" s="4" t="n"/>
-      <c r="G179" s="4" t="n"/>
-      <c r="H179" s="4" t="n"/>
-      <c r="I179" s="4" t="n"/>
-      <c r="J179" s="4" t="n"/>
-      <c r="K179" s="4" t="n"/>
-      <c r="L179" s="4" t="n"/>
-      <c r="M179" s="4" t="n"/>
-      <c r="N179" s="4" t="n"/>
-      <c r="O179" s="4" t="n"/>
-      <c r="P179" s="4" t="n"/>
-      <c r="Q179" s="5" t="n"/>
-    </row>
-    <row r="180" ht="47" customHeight="1">
+    <row r="179" ht="36" customHeight="1">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B179" s="15" t="inlineStr">
+        <is>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>TC_10.005</t>
+        </is>
+      </c>
+      <c r="D179" s="15" t="inlineStr">
+        <is>
+          <t>Trưởng phòng công ty khác trùng phòng ban không duyệt được</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F179" s="15" t="inlineStr">
+        <is>
+          <t>Trưởng phòng E4 thuộc công ty 4 nhưng được gán quản lý một phòng ban trùng với phòng của phiếu X (công ty 1).</t>
+        </is>
+      </c>
+      <c r="G179" s="15" t="inlineStr">
+        <is>
+          <t>1. Dùng công cụ kiểm thử gọi chức năng duyệt X bằng E4.</t>
+        </is>
+      </c>
+      <c r="H179" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>- Bị từ chối "Bạn không có quyền duyệt bước này."
+- Lưu ý: ERP cho qua trường hợp này; hệ thống mới đã chặn.</t>
+        </is>
+      </c>
+      <c r="J179" s="15" t="inlineStr"/>
+      <c r="K179" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L179" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M179" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N179" s="15" t="inlineStr"/>
+      <c r="O179" s="16" t="inlineStr"/>
+      <c r="P179" s="16" t="inlineStr"/>
+      <c r="Q179" s="16" t="inlineStr"/>
+    </row>
+    <row r="180" ht="35" customHeight="1">
       <c r="A180" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11679,43 +11734,45 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>LỊCH SỬ THAY ĐỔI</t>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
         </is>
       </c>
       <c r="C180" s="16" t="inlineStr">
         <is>
-          <t>TC_11.001</t>
+          <t>TC_10.006</t>
         </is>
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>Khối Lịch sử thay đổi thu gọn sẵn có đếm số mốc</t>
+          <t>Bộ lọc không làm lộ phiếu ngoài phạm vi ở lối "chờ duyệt"</t>
         </is>
       </c>
       <c r="E180" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>Phiếu đã qua tạo và Trưởng phòng duyệt.</t>
+          <t>Trưởng phòng E (có thêm Kế toán kho để thấy menu) quản lý P1. P2 có phiếu Chờ TP duyệt do nhân viên X lập.</t>
         </is>
       </c>
       <c r="G180" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết phiếu.</t>
+          <t>1. E mở lối vào "chờ duyệt".
+2. Lọc Người tạo = X.
+3. Lọc Trạng thái = Chờ TP duyệt.</t>
         </is>
       </c>
       <c r="H180" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Người tạo: X
+Trạng thái: Chờ TP duyệt</t>
         </is>
       </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>- Khối "Lịch sử thay đổi" đang thu gọn, cạnh tiêu đề có số 2.
-- Bấm "Xem lịch sử" thì mở ra; nút đổi thành "Thu gọn" và có thêm nút "Làm mới".</t>
+          <t>- Không ra phiếu nào của P2.</t>
         </is>
       </c>
       <c r="J180" s="15" t="inlineStr"/>
@@ -11739,7 +11796,7 @@
       <c r="P180" s="16" t="inlineStr"/>
       <c r="Q180" s="16" t="inlineStr"/>
     </row>
-    <row r="181" ht="43" customHeight="1">
+    <row r="181" ht="52" customHeight="1">
       <c r="A181" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11747,42 +11804,45 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>LỊCH SỬ THAY ĐỔI</t>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
         </is>
       </c>
       <c r="C181" s="16" t="inlineStr">
         <is>
-          <t>TC_11.002</t>
+          <t>TC_10.007</t>
         </is>
       </c>
       <c r="D181" s="15" t="inlineStr">
         <is>
-          <t>Dòng nhắc thao tác bên cổng cũ</t>
+          <t>Phiếu Không duyệt hiện theo phạm vi quyền</t>
         </is>
       </c>
       <c r="E181" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F181" s="15" t="inlineStr">
         <is>
-          <t>Mở khối Lịch sử thay đổi.</t>
+          <t>Phiếu X do B lập, bị Trưởng phòng E từ chối. C có quyền Xem theo công ty.</t>
         </is>
       </c>
       <c r="G181" s="15" t="inlineStr">
         <is>
-          <t>1. Đọc dòng nhắc đầu khối.</t>
+          <t>1. C lọc Trạng thái = Không duyệt.
+2. E (chỉ có quyền Trưởng phòng duyệt) mở danh sách.</t>
         </is>
       </c>
       <c r="H181" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trạng thái: Không duyệt</t>
         </is>
       </c>
       <c r="I181" s="15" t="inlineStr">
         <is>
-          <t>- Ghi "Lịch sử chỉ ghi các thao tác làm trên hệ thống này. Phiếu duyệt hoặc từ chối bên cổng ERP cũ sẽ không có trong danh sách."</t>
+          <t>- C thấy X.
+- E vẫn thấy X (người đã từ chối), bấm vào mở được.
+- Lưu ý: ERP giấu phiếu Không duyệt với mọi người trừ người lập; hệ thống mới đã bỏ luật này.</t>
         </is>
       </c>
       <c r="J181" s="15" t="inlineStr"/>
@@ -11806,7 +11866,7 @@
       <c r="P181" s="16" t="inlineStr"/>
       <c r="Q181" s="16" t="inlineStr"/>
     </row>
-    <row r="182" ht="44" customHeight="1">
+    <row r="182" ht="71" customHeight="1">
       <c r="A182" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -11814,33 +11874,34 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>LỊCH SỬ THAY ĐỔI</t>
+          <t>CÔ LẬP DỮ LIỆU &amp; THAO TÁC ĐỒNG THỜI</t>
         </is>
       </c>
       <c r="C182" s="16" t="inlineStr">
         <is>
-          <t>TC_11.003</t>
+          <t>TC_10.008</t>
         </is>
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>Phiếu xử lý bên cổng cũ không có lịch sử</t>
+          <t>Quyền tổng công ty thấy và mở phiếu công ty khác nhưng không duyệt được</t>
         </is>
       </c>
       <c r="E182" s="16" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
-          <t>Phiếu cũ được lập và duyệt hoàn toàn bên ERP.</t>
+          <t>B có quyền Xem theo tổng công ty và quyền Kế toán kho (công ty 1). Phiếu W thuộc công ty 4, đang Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G182" s="15" t="inlineStr">
         <is>
-          <t>1. Mở chi tiết, mở Lịch sử thay đổi.
-2. Ở danh sách chọn Hành động &gt; Lịch sử.</t>
+          <t>1. B tìm W ở danh sách lối vào thường.
+2. Bấm mở W.
+3. B mở lối vào "chờ duyệt".</t>
         </is>
       </c>
       <c r="H182" s="15" t="inlineStr">
@@ -11850,9 +11911,9 @@
       </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>- Cả hai nơi ghi "Chưa có lịch sử thao tác nào."
-- Không có badge số cạnh tiêu đề.
-- Đây là đúng thiết kế, không phải lỗi mất dữ liệu.</t>
+          <t>- Bước 1: W CÓ trong danh sách (danh sách và màn chi tiết nay khớp nhau, Redmine #11534).
+- Bước 2: xem được nội dung W, KHÔNG có nút duyệt / từ chối (khác công ty).
+- Bước 3: W KHÔNG có trong danh sách chờ duyệt.</t>
         </is>
       </c>
       <c r="J182" s="15" t="inlineStr"/>
@@ -11876,118 +11937,74 @@
       <c r="P182" s="16" t="inlineStr"/>
       <c r="Q182" s="16" t="inlineStr"/>
     </row>
-    <row r="183" ht="65" customHeight="1">
-      <c r="A183" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B183" s="15" t="inlineStr">
+    <row r="183" ht="26" customHeight="1">
+      <c r="A183" s="13" t="n"/>
+      <c r="B183" s="13" t="n"/>
+      <c r="C183" s="14" t="inlineStr">
+        <is>
+          <t>XI. LỊCH SỬ THAY ĐỔI</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="4" t="n"/>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
+      <c r="L183" s="4" t="n"/>
+      <c r="M183" s="4" t="n"/>
+      <c r="N183" s="4" t="n"/>
+      <c r="O183" s="4" t="n"/>
+      <c r="P183" s="4" t="n"/>
+      <c r="Q183" s="5" t="n"/>
+    </row>
+    <row r="184" ht="47" customHeight="1">
+      <c r="A184" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="inlineStr">
         <is>
           <t>LỊCH SỬ THAY ĐỔI</t>
         </is>
       </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>TC_11.004</t>
-        </is>
-      </c>
-      <c r="D183" s="15" t="inlineStr">
-        <is>
-          <t>Lịch sử đủ vòng đời, mới nhất ở trên</t>
-        </is>
-      </c>
-      <c r="E183" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F183" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu tạo trên hệ thống mới, qua TP duyệt, BGĐ duyệt, Kế toán sửa ngày rồi duyệt.</t>
-        </is>
-      </c>
-      <c r="G183" s="15" t="inlineStr">
-        <is>
-          <t>1. Mở Lịch sử thay đổi.</t>
-        </is>
-      </c>
-      <c r="H183" s="15" t="inlineStr">
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>TC_11.001</t>
+        </is>
+      </c>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>Khối Lịch sử thay đổi thu gọn sẵn có đếm số mốc</t>
+        </is>
+      </c>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F184" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu đã qua tạo và Trưởng phòng duyệt.</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở chi tiết phiếu.</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I183" s="15" t="inlineStr">
-        <is>
-          <t>- 5 dòng theo thứ tự từ trên xuống: Kế toán duyệt, Chỉnh sửa, Ban giám đốc duyệt, Trưởng phòng duyệt, Tạo phiếu.
-- Mỗi dòng có thời điểm dd/mm/yyyy hh:mm và "Người thực hiện: &lt;tên&gt; - &lt;phòng ban&gt;".</t>
-        </is>
-      </c>
-      <c r="J183" s="15" t="inlineStr"/>
-      <c r="K183" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L183" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M183" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N183" s="15" t="inlineStr"/>
-      <c r="O183" s="16" t="inlineStr"/>
-      <c r="P183" s="16" t="inlineStr"/>
-      <c r="Q183" s="16" t="inlineStr"/>
-    </row>
-    <row r="184" ht="35" customHeight="1">
-      <c r="A184" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B184" s="15" t="inlineStr">
-        <is>
-          <t>LỊCH SỬ THAY ĐỔI</t>
-        </is>
-      </c>
-      <c r="C184" s="16" t="inlineStr">
-        <is>
-          <t>TC_11.005</t>
-        </is>
-      </c>
-      <c r="D184" s="15" t="inlineStr">
-        <is>
-          <t>Dòng Tạo phiếu ghi giá trị ban đầu</t>
-        </is>
-      </c>
-      <c r="E184" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F184" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu vừa tạo, Ngày hẹn trả mới 05/10/2026, Ghi chú "Khách chưa nghiệm thu xong", 1 file.</t>
-        </is>
-      </c>
-      <c r="G184" s="15" t="inlineStr">
-        <is>
-          <t>1. Mở Lịch sử thay đổi.</t>
-        </is>
-      </c>
-      <c r="H184" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>- Dòng "Tạo phiếu" liệt kê Trạng thái: Chờ TP duyệt, Ngày hẹn trả mới: 05/10/2026, Ghi chú, File đính kèm.</t>
+          <t>- Khối "Lịch sử thay đổi" đang thu gọn, cạnh tiêu đề có số 2.
+- Bấm "Xem lịch sử" thì mở ra; nút đổi thành "Thu gọn" và có thêm nút "Làm mới".</t>
         </is>
       </c>
       <c r="J184" s="15" t="inlineStr"/>
@@ -12011,7 +12028,7 @@
       <c r="P184" s="16" t="inlineStr"/>
       <c r="Q184" s="16" t="inlineStr"/>
     </row>
-    <row r="185" ht="34" customHeight="1">
+    <row r="185" ht="39" customHeight="1">
       <c r="A185" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12024,27 +12041,28 @@
       </c>
       <c r="C185" s="16" t="inlineStr">
         <is>
-          <t>TC_11.006</t>
+          <t>TC_11.002</t>
         </is>
       </c>
       <c r="D185" s="15" t="inlineStr">
         <is>
-          <t>Dòng duyệt ghi đổi trạng thái</t>
+          <t>Nút Bộ lọc của lịch sử chỉ hiện khi có mốc</t>
         </is>
       </c>
       <c r="E185" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="F185" s="15" t="inlineStr">
         <is>
-          <t>Phiếu vừa được TP duyệt sang Chờ KT duyệt.</t>
+          <t>Phiếu A có 2 mốc lịch sử; phiếu B lập và xử lý hoàn toàn bên cổng ERP cũ (không có mốc nào).</t>
         </is>
       </c>
       <c r="G185" s="15" t="inlineStr">
         <is>
-          <t>1. Mở Lịch sử thay đổi.</t>
+          <t>1. Mở Lịch sử thay đổi của A.
+2. Mở Lịch sử thay đổi của B.</t>
         </is>
       </c>
       <c r="H185" s="15" t="inlineStr">
@@ -12054,7 +12072,8 @@
       </c>
       <c r="I185" s="15" t="inlineStr">
         <is>
-          <t>- Dòng "Trưởng phòng duyệt" ghi Trạng thái: Chờ TP duyệt sang Chờ KT duyệt.</t>
+          <t>- A: có nút "Bộ lọc" phía trên danh sách mốc.
+- B: KHÔNG có nút "Bộ lọc", chỉ có dòng "Chưa có lịch sử thao tác nào."</t>
         </is>
       </c>
       <c r="J185" s="15" t="inlineStr"/>
@@ -12078,7 +12097,7 @@
       <c r="P185" s="16" t="inlineStr"/>
       <c r="Q185" s="16" t="inlineStr"/>
     </row>
-    <row r="186" ht="57" customHeight="1">
+    <row r="186" ht="44" customHeight="1">
       <c r="A186" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12091,12 +12110,12 @@
       </c>
       <c r="C186" s="16" t="inlineStr">
         <is>
-          <t>TC_11.007</t>
+          <t>TC_11.003</t>
         </is>
       </c>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>Dòng Không duyệt hiện lý do</t>
+          <t>Phiếu xử lý bên cổng cũ không có lịch sử</t>
         </is>
       </c>
       <c r="E186" s="16" t="inlineStr">
@@ -12106,12 +12125,13 @@
       </c>
       <c r="F186" s="15" t="inlineStr">
         <is>
-          <t>Phiếu bị từ chối với lý do "Chưa trả hàng kỳ trước".</t>
+          <t>Phiếu cũ được lập và duyệt hoàn toàn bên ERP.</t>
         </is>
       </c>
       <c r="G186" s="15" t="inlineStr">
         <is>
-          <t>1. Mở Lịch sử thay đổi (ở màn chi tiết và ở popup danh sách).</t>
+          <t>1. Mở chi tiết, mở Lịch sử thay đổi.
+2. Ở danh sách chọn Hành động &gt; Lịch sử.</t>
         </is>
       </c>
       <c r="H186" s="15" t="inlineStr">
@@ -12121,9 +12141,9 @@
       </c>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>- Dòng "Không duyệt" màu đỏ, Trạng thái đổi sang Không duyệt.
-- Khối ghi chú của dòng hiện "Chưa trả hàng kỳ trước".
-- Nội dung ở popup danh sách giống hệt ở màn chi tiết.</t>
+          <t>- Cả hai nơi ghi "Chưa có lịch sử thao tác nào."
+- Không có badge số cạnh tiêu đề.
+- Đây là đúng thiết kế, không phải lỗi mất dữ liệu.</t>
         </is>
       </c>
       <c r="J186" s="15" t="inlineStr"/>
@@ -12147,7 +12167,7 @@
       <c r="P186" s="16" t="inlineStr"/>
       <c r="Q186" s="16" t="inlineStr"/>
     </row>
-    <row r="187" ht="34" customHeight="1">
+    <row r="187" ht="68" customHeight="1">
       <c r="A187" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12160,28 +12180,27 @@
       </c>
       <c r="C187" s="16" t="inlineStr">
         <is>
-          <t>TC_11.008</t>
+          <t>TC_11.004</t>
         </is>
       </c>
       <c r="D187" s="15" t="inlineStr">
         <is>
-          <t>Kế toán duyệt không đổi ngày thì không có dòng Chỉnh sửa</t>
+          <t>Lịch sử đủ vòng đời, mới nhất ở trên</t>
         </is>
       </c>
       <c r="E187" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F187" s="15" t="inlineStr">
         <is>
-          <t>Phiếu Chờ KT duyệt.</t>
+          <t>Phiếu tạo trên hệ thống mới, qua TP duyệt, BGĐ duyệt, Kế toán sửa ngày rồi duyệt.</t>
         </is>
       </c>
       <c r="G187" s="15" t="inlineStr">
         <is>
-          <t>1. Kế toán duyệt giữ nguyên ngày.
-2. Mở lịch sử.</t>
+          <t>1. Mở Lịch sử thay đổi.</t>
         </is>
       </c>
       <c r="H187" s="15" t="inlineStr">
@@ -12191,7 +12210,8 @@
       </c>
       <c r="I187" s="15" t="inlineStr">
         <is>
-          <t>- Không có dòng "Chỉnh sửa", chỉ thêm dòng "Kế toán duyệt".</t>
+          <t>- 5 dòng theo thứ tự từ trên xuống: Kế toán duyệt, Thay đổi thông tin, Ban giám đốc duyệt, Trưởng phòng duyệt, Tạo phiếu.
+- Mỗi dòng có thời điểm dd/mm/yyyy hh:mm và "Người thực hiện: &lt;tên&gt; - &lt;phòng ban&gt;".</t>
         </is>
       </c>
       <c r="J187" s="15" t="inlineStr"/>
@@ -12215,7 +12235,7 @@
       <c r="P187" s="16" t="inlineStr"/>
       <c r="Q187" s="16" t="inlineStr"/>
     </row>
-    <row r="188" ht="34" customHeight="1">
+    <row r="188" ht="35" customHeight="1">
       <c r="A188" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12228,12 +12248,12 @@
       </c>
       <c r="C188" s="16" t="inlineStr">
         <is>
-          <t>TC_11.009</t>
+          <t>TC_11.005</t>
         </is>
       </c>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>Popup Lịch sử ở danh sách</t>
+          <t>Dòng Tạo phiếu ghi giá trị ban đầu</t>
         </is>
       </c>
       <c r="E188" s="16" t="inlineStr">
@@ -12243,12 +12263,12 @@
       </c>
       <c r="F188" s="15" t="inlineStr">
         <is>
-          <t>Có phiếu có 3 mốc lịch sử.</t>
+          <t>Phiếu vừa tạo, Ngày hẹn trả mới 05/10/2026, Ghi chú "Khách chưa nghiệm thu xong", 1 file.</t>
         </is>
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>1. Chọn Hành động &gt; Lịch sử ở dòng đó.</t>
+          <t>1. Mở Lịch sử thay đổi.</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr">
@@ -12258,7 +12278,7 @@
       </c>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>- Popup "Lịch sử yêu cầu gia hạn hàng mượn" kèm mã phiếu, hiện đủ 3 mốc.</t>
+          <t>- Dòng "Tạo phiếu" liệt kê Trạng thái: Chờ TP duyệt, Ngày hẹn trả mới: 05/10/2026, Ghi chú, File đính kèm.</t>
         </is>
       </c>
       <c r="J188" s="15" t="inlineStr"/>
@@ -12282,7 +12302,7 @@
       <c r="P188" s="16" t="inlineStr"/>
       <c r="Q188" s="16" t="inlineStr"/>
     </row>
-    <row r="189" ht="50" customHeight="1">
+    <row r="189" ht="34" customHeight="1">
       <c r="A189" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12295,29 +12315,27 @@
       </c>
       <c r="C189" s="16" t="inlineStr">
         <is>
-          <t>TC_11.010</t>
+          <t>TC_11.006</t>
         </is>
       </c>
       <c r="D189" s="15" t="inlineStr">
         <is>
-          <t>Bộ lọc trong lịch sử</t>
+          <t>Dòng duyệt ghi đổi trạng thái</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F189" s="15" t="inlineStr">
         <is>
-          <t>Phiếu có 5 mốc lịch sử do 4 người thực hiện.</t>
+          <t>Phiếu vừa được TP duyệt sang Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="G189" s="15" t="inlineStr">
         <is>
-          <t>1. Mở lịch sử, bấm "Bộ lọc".
-2. Chọn Loại hành động = Không duyệt (khi phiếu không có mốc này thì chọn Chỉnh sửa).
-3. Chọn Người thực hiện = Kế toán G.</t>
+          <t>1. Mở Lịch sử thay đổi.</t>
         </is>
       </c>
       <c r="H189" s="15" t="inlineStr">
@@ -12327,8 +12345,7 @@
       </c>
       <c r="I189" s="15" t="inlineStr">
         <is>
-          <t>- Có các ô Loại hành động, Người thực hiện, Từ ngày, Đến ngày.
-- Lọc đúng các mốc khớp; không khớp thì ghi "Không có lịch sử phù hợp bộ lọc."</t>
+          <t>- Dòng "Trưởng phòng duyệt" ghi Trạng thái: Chờ TP duyệt sang Chờ KT duyệt.</t>
         </is>
       </c>
       <c r="J189" s="15" t="inlineStr"/>
@@ -12352,7 +12369,7 @@
       <c r="P189" s="16" t="inlineStr"/>
       <c r="Q189" s="16" t="inlineStr"/>
     </row>
-    <row r="190" ht="34" customHeight="1">
+    <row r="190" ht="57" customHeight="1">
       <c r="A190" s="15" t="inlineStr">
         <is>
           <t>YC gia hạn hàng mượn</t>
@@ -12365,27 +12382,27 @@
       </c>
       <c r="C190" s="16" t="inlineStr">
         <is>
-          <t>TC_11.011</t>
+          <t>TC_11.007</t>
         </is>
       </c>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>Làm mới lịch sử sau thao tác</t>
+          <t>Dòng Không duyệt hiện lý do</t>
         </is>
       </c>
       <c r="E190" s="16" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="F190" s="15" t="inlineStr">
         <is>
-          <t>Đang mở khối lịch sử ở tab 1; tab 2 vừa có người duyệt phiếu.</t>
+          <t>Phiếu bị từ chối với lý do "Chưa trả hàng kỳ trước".</t>
         </is>
       </c>
       <c r="G190" s="15" t="inlineStr">
         <is>
-          <t>1. Bấm "Làm mới" trong khối lịch sử tab 1.</t>
+          <t>1. Mở Lịch sử thay đổi (ở màn chi tiết và ở popup danh sách).</t>
         </is>
       </c>
       <c r="H190" s="15" t="inlineStr">
@@ -12395,7 +12412,9 @@
       </c>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>- Mốc duyệt mới hiện lên đầu danh sách.</t>
+          <t>- Dòng "Không duyệt" màu đỏ, Trạng thái đổi sang Không duyệt.
+- Khối ghi chú của dòng hiện "Chưa trả hàng kỳ trước".
+- Nội dung ở popup danh sách giống hệt ở màn chi tiết.</t>
         </is>
       </c>
       <c r="J190" s="15" t="inlineStr"/>
@@ -12419,61 +12438,335 @@
       <c r="P190" s="16" t="inlineStr"/>
       <c r="Q190" s="16" t="inlineStr"/>
     </row>
-    <row r="191" ht="26" customHeight="1">
-      <c r="A191" s="13" t="n"/>
-      <c r="B191" s="13" t="n"/>
-      <c r="C191" s="14" t="inlineStr">
+    <row r="191" ht="34" customHeight="1">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>LỊCH SỬ THAY ĐỔI</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>TC_11.008</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>Kế toán duyệt không đổi ngày thì không có dòng Thay đổi thông tin</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F191" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu Chờ KT duyệt.</t>
+        </is>
+      </c>
+      <c r="G191" s="15" t="inlineStr">
+        <is>
+          <t>1. Kế toán duyệt giữ nguyên ngày.
+2. Mở lịch sử.</t>
+        </is>
+      </c>
+      <c r="H191" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I191" s="15" t="inlineStr">
+        <is>
+          <t>- Không có dòng "Thay đổi thông tin", chỉ thêm dòng "Kế toán duyệt".</t>
+        </is>
+      </c>
+      <c r="J191" s="15" t="inlineStr"/>
+      <c r="K191" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L191" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M191" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N191" s="15" t="inlineStr"/>
+      <c r="O191" s="16" t="inlineStr"/>
+      <c r="P191" s="16" t="inlineStr"/>
+      <c r="Q191" s="16" t="inlineStr"/>
+    </row>
+    <row r="192" ht="34" customHeight="1">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>LỊCH SỬ THAY ĐỔI</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>TC_11.009</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>Popup Lịch sử ở danh sách</t>
+        </is>
+      </c>
+      <c r="E192" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F192" s="15" t="inlineStr">
+        <is>
+          <t>Có phiếu có 3 mốc lịch sử.</t>
+        </is>
+      </c>
+      <c r="G192" s="15" t="inlineStr">
+        <is>
+          <t>1. Chọn Hành động &gt; Lịch sử ở dòng đó.</t>
+        </is>
+      </c>
+      <c r="H192" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>- Popup "Lịch sử yêu cầu gia hạn hàng mượn" kèm mã phiếu, hiện đủ 3 mốc.</t>
+        </is>
+      </c>
+      <c r="J192" s="15" t="inlineStr"/>
+      <c r="K192" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L192" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M192" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N192" s="15" t="inlineStr"/>
+      <c r="O192" s="16" t="inlineStr"/>
+      <c r="P192" s="16" t="inlineStr"/>
+      <c r="Q192" s="16" t="inlineStr"/>
+    </row>
+    <row r="193" ht="74" customHeight="1">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="inlineStr">
+        <is>
+          <t>LỊCH SỬ THAY ĐỔI</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="inlineStr">
+        <is>
+          <t>TC_11.010</t>
+        </is>
+      </c>
+      <c r="D193" s="15" t="inlineStr">
+        <is>
+          <t>Bộ lọc trong lịch sử</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F193" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu có 5 mốc lịch sử do 4 người thực hiện.</t>
+        </is>
+      </c>
+      <c r="G193" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở lịch sử, bấm "Bộ lọc".
+2. Mở ô Loại hành động.
+3. Chọn Loại hành động = Thay đổi thông tin.
+4. Chọn Người thực hiện = Kế toán G.</t>
+        </is>
+      </c>
+      <c r="H193" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I193" s="15" t="inlineStr">
+        <is>
+          <t>- Có các ô Loại hành động, Người thực hiện, Từ ngày, Đến ngày.
+- Ô Loại hành động chỉ liệt kê những loại ĐÃ CÓ trong lịch sử của chính phiếu này.
+- Lọc đúng các mốc khớp; không khớp thì ghi "Không có lịch sử phù hợp bộ lọc."</t>
+        </is>
+      </c>
+      <c r="J193" s="15" t="inlineStr"/>
+      <c r="K193" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L193" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M193" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N193" s="15" t="inlineStr"/>
+      <c r="O193" s="16" t="inlineStr"/>
+      <c r="P193" s="16" t="inlineStr"/>
+      <c r="Q193" s="16" t="inlineStr"/>
+    </row>
+    <row r="194" ht="34" customHeight="1">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>LỊCH SỬ THAY ĐỔI</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>TC_11.011</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>Làm mới lịch sử sau thao tác</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F194" s="15" t="inlineStr">
+        <is>
+          <t>Đang mở khối lịch sử ở tab 1; tab 2 vừa có người duyệt phiếu.</t>
+        </is>
+      </c>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>1. Bấm "Làm mới" trong khối lịch sử tab 1.</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>- Mốc duyệt mới hiện lên đầu danh sách.</t>
+        </is>
+      </c>
+      <c r="J194" s="15" t="inlineStr"/>
+      <c r="K194" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L194" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M194" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N194" s="15" t="inlineStr"/>
+      <c r="O194" s="16" t="inlineStr"/>
+      <c r="P194" s="16" t="inlineStr"/>
+      <c r="Q194" s="16" t="inlineStr"/>
+    </row>
+    <row r="195" ht="26" customHeight="1">
+      <c r="A195" s="13" t="n"/>
+      <c r="B195" s="13" t="n"/>
+      <c r="C195" s="14" t="inlineStr">
         <is>
           <t>XII. LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
         </is>
       </c>
-      <c r="D191" s="4" t="n"/>
-      <c r="E191" s="4" t="n"/>
-      <c r="F191" s="4" t="n"/>
-      <c r="G191" s="4" t="n"/>
-      <c r="H191" s="4" t="n"/>
-      <c r="I191" s="4" t="n"/>
-      <c r="J191" s="4" t="n"/>
-      <c r="K191" s="4" t="n"/>
-      <c r="L191" s="4" t="n"/>
-      <c r="M191" s="4" t="n"/>
-      <c r="N191" s="4" t="n"/>
-      <c r="O191" s="4" t="n"/>
-      <c r="P191" s="4" t="n"/>
-      <c r="Q191" s="5" t="n"/>
-    </row>
-    <row r="192" ht="77" customHeight="1">
-      <c r="A192" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B192" s="15" t="inlineStr">
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
+      <c r="Q195" s="5" t="n"/>
+    </row>
+    <row r="196" ht="77" customHeight="1">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
         <is>
           <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
         </is>
       </c>
-      <c r="C192" s="16" t="inlineStr">
+      <c r="C196" s="16" t="inlineStr">
         <is>
           <t>TC_12.001</t>
         </is>
       </c>
-      <c r="D192" s="15" t="inlineStr">
+      <c r="D196" s="15" t="inlineStr">
         <is>
           <t>Luồng đầy đủ dưới hạn mức</t>
         </is>
       </c>
-      <c r="E192" s="16" t="inlineStr">
+      <c r="E196" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F192" s="15" t="inlineStr">
+      <c r="F196" s="15" t="inlineStr">
         <is>
           <t>Nhân viên A (phòng P1) có phiếu mượn M hạn 23/09/2026, còn nợ 5,000,000; hạn mức 20,000,000.</t>
         </is>
       </c>
-      <c r="G192" s="15" t="inlineStr">
+      <c r="G196" s="15" t="inlineStr">
         <is>
           <t>1. A lập phiếu gia hạn M sang 05/10/2026.
 2. Trưởng phòng E duyệt.
@@ -12481,12 +12774,12 @@
 4. Kiểm tra M và popup chọn phiếu của A.</t>
         </is>
       </c>
-      <c r="H192" s="15" t="inlineStr">
+      <c r="H196" s="15" t="inlineStr">
         <is>
           <t>Ngày hẹn trả mới: 05/10/2026</t>
         </is>
       </c>
-      <c r="I192" s="15" t="inlineStr">
+      <c r="I196" s="15" t="inlineStr">
         <is>
           <t>- Sau bước 1: Chờ TP duyệt; M vẫn 23/09.
 - Sau bước 2: Chờ KT duyệt (bỏ qua BGĐ); M vẫn 23/09.
@@ -12494,59 +12787,59 @@
 - M quay lại popup chọn phiếu của A với Ngày hẹn trả 05/10/2026 (nếu còn trước ngày trần).</t>
         </is>
       </c>
-      <c r="J192" s="15" t="inlineStr"/>
-      <c r="K192" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L192" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M192" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N192" s="15" t="inlineStr"/>
-      <c r="O192" s="16" t="inlineStr"/>
-      <c r="P192" s="16" t="inlineStr"/>
-      <c r="Q192" s="16" t="inlineStr"/>
-    </row>
-    <row r="193" ht="59" customHeight="1">
-      <c r="A193" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B193" s="15" t="inlineStr">
+      <c r="J196" s="15" t="inlineStr"/>
+      <c r="K196" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L196" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M196" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N196" s="15" t="inlineStr"/>
+      <c r="O196" s="16" t="inlineStr"/>
+      <c r="P196" s="16" t="inlineStr"/>
+      <c r="Q196" s="16" t="inlineStr"/>
+    </row>
+    <row r="197" ht="59" customHeight="1">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B197" s="15" t="inlineStr">
         <is>
           <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
         </is>
       </c>
-      <c r="C193" s="16" t="inlineStr">
+      <c r="C197" s="16" t="inlineStr">
         <is>
           <t>TC_12.002</t>
         </is>
       </c>
-      <c r="D193" s="15" t="inlineStr">
+      <c r="D197" s="15" t="inlineStr">
         <is>
           <t>Luồng đầy đủ vượt hạn mức</t>
         </is>
       </c>
-      <c r="E193" s="16" t="inlineStr">
+      <c r="E197" s="16" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F193" s="15" t="inlineStr">
+      <c r="F197" s="15" t="inlineStr">
         <is>
           <t>Phiếu mượn M còn nợ 25,000,000; hạn mức 20,000,000.</t>
         </is>
       </c>
-      <c r="G193" s="15" t="inlineStr">
+      <c r="G197" s="15" t="inlineStr">
         <is>
           <t>1. Lập phiếu gia hạn.
 2. TP duyệt.
@@ -12554,293 +12847,16 @@
 4. KT sửa ngày rồi duyệt.</t>
         </is>
       </c>
-      <c r="H193" s="15" t="inlineStr">
+      <c r="H197" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I193" s="15" t="inlineStr">
+      <c r="I197" s="15" t="inlineStr">
         <is>
           <t>- Trạng thái đi đúng: Chờ TP duyệt, Chờ BGĐ duyệt, Chờ KT duyệt, Đã duyệt.
 - M đổi hạn đúng ngày Kế toán đã sửa.
 - Lịch sử duyệt ở chi tiết có đủ 3 cấp; Lịch sử thay đổi có 5 mốc.</t>
-        </is>
-      </c>
-      <c r="J193" s="15" t="inlineStr"/>
-      <c r="K193" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L193" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M193" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N193" s="15" t="inlineStr"/>
-      <c r="O193" s="16" t="inlineStr"/>
-      <c r="P193" s="16" t="inlineStr"/>
-      <c r="Q193" s="16" t="inlineStr"/>
-    </row>
-    <row r="194" ht="53" customHeight="1">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B194" s="15" t="inlineStr">
-        <is>
-          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>TC_12.003</t>
-        </is>
-      </c>
-      <c r="D194" s="15" t="inlineStr">
-        <is>
-          <t>Từ chối rồi lập phiếu mới</t>
-        </is>
-      </c>
-      <c r="E194" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F194" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu gia hạn X của M bị TP từ chối.</t>
-        </is>
-      </c>
-      <c r="G194" s="15" t="inlineStr">
-        <is>
-          <t>1. Người lập mở X tìm cách gửi lại.
-2. Vào Tạo mới, chọn lại M, gửi phiếu mới.
-3. TP và KT duyệt phiếu mới.</t>
-        </is>
-      </c>
-      <c r="H194" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I194" s="15" t="inlineStr">
-        <is>
-          <t>- X không có nút gửi lại / sửa, giữ Không duyệt.
-- M có trong popup chọn phiếu ngay sau khi X bị từ chối.
-- Phiếu mới đi hết luồng, M đổi hạn; X vẫn Không duyệt.</t>
-        </is>
-      </c>
-      <c r="J194" s="15" t="inlineStr"/>
-      <c r="K194" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L194" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M194" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N194" s="15" t="inlineStr"/>
-      <c r="O194" s="16" t="inlineStr"/>
-      <c r="P194" s="16" t="inlineStr"/>
-      <c r="Q194" s="16" t="inlineStr"/>
-    </row>
-    <row r="195" ht="46" customHeight="1">
-      <c r="A195" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B195" s="15" t="inlineStr">
-        <is>
-          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>TC_12.004</t>
-        </is>
-      </c>
-      <c r="D195" s="15" t="inlineStr">
-        <is>
-          <t>Gia hạn hai lần liên tiếp cùng phiếu mượn</t>
-        </is>
-      </c>
-      <c r="E195" s="16" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F195" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu mượn M hạn 23/09. Số ngày mượn tối đa 7.</t>
-        </is>
-      </c>
-      <c r="G195" s="15" t="inlineStr">
-        <is>
-          <t>1. Lập và duyệt xong phiếu gia hạn M sang 03/10.
-2. Lập tiếp phiếu gia hạn M.</t>
-        </is>
-      </c>
-      <c r="H195" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I195" s="15" t="inlineStr">
-        <is>
-          <t>- Lần 2, Ngày hẹn trả hiện 03/10/2026; lịch chỉ cho chọn từ 04/10 đến ngày trần.
-- Không lập được phiếu có ngày mới trùng hoặc trước 03/10.</t>
-        </is>
-      </c>
-      <c r="J195" s="15" t="inlineStr"/>
-      <c r="K195" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L195" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M195" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N195" s="15" t="inlineStr"/>
-      <c r="O195" s="16" t="inlineStr"/>
-      <c r="P195" s="16" t="inlineStr"/>
-      <c r="Q195" s="16" t="inlineStr"/>
-    </row>
-    <row r="196" ht="34" customHeight="1">
-      <c r="A196" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B196" s="15" t="inlineStr">
-        <is>
-          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
-        </is>
-      </c>
-      <c r="C196" s="16" t="inlineStr">
-        <is>
-          <t>TC_12.005</t>
-        </is>
-      </c>
-      <c r="D196" s="15" t="inlineStr">
-        <is>
-          <t>Kiểm tra chéo với màn Hàng sắp hết hạn mượn / Danh sách hàng mượn</t>
-        </is>
-      </c>
-      <c r="E196" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F196" s="15" t="inlineStr">
-        <is>
-          <t>Vừa duyệt xong phiếu gia hạn M sang 05/10/2026.</t>
-        </is>
-      </c>
-      <c r="G196" s="15" t="inlineStr">
-        <is>
-          <t>1. Mở Tài chính &gt; Mượn hàng &gt; Danh sách hàng mượn, tìm hàng của M.
-2. Mở Hàng sắp hết hạn mượn.</t>
-        </is>
-      </c>
-      <c r="H196" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I196" s="15" t="inlineStr">
-        <is>
-          <t>- Hạn trả của hàng thuộc M hiện 05/10/2026.
-- M không còn nằm trong diện sắp hết hạn theo hạn cũ.</t>
-        </is>
-      </c>
-      <c r="J196" s="15" t="inlineStr"/>
-      <c r="K196" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="L196" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M196" s="16" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N196" s="15" t="inlineStr"/>
-      <c r="O196" s="16" t="inlineStr"/>
-      <c r="P196" s="16" t="inlineStr"/>
-      <c r="Q196" s="16" t="inlineStr"/>
-    </row>
-    <row r="197" ht="34" customHeight="1">
-      <c r="A197" s="15" t="inlineStr">
-        <is>
-          <t>YC gia hạn hàng mượn</t>
-        </is>
-      </c>
-      <c r="B197" s="15" t="inlineStr">
-        <is>
-          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
-        </is>
-      </c>
-      <c r="C197" s="16" t="inlineStr">
-        <is>
-          <t>TC_12.006</t>
-        </is>
-      </c>
-      <c r="D197" s="15" t="inlineStr">
-        <is>
-          <t>Từ chối không đụng phiếu mượn</t>
-        </is>
-      </c>
-      <c r="E197" s="16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F197" s="15" t="inlineStr">
-        <is>
-          <t>Phiếu gia hạn M đã qua TP, đang Chờ KT duyệt.</t>
-        </is>
-      </c>
-      <c r="G197" s="15" t="inlineStr">
-        <is>
-          <t>1. Kế toán từ chối.
-2. Mở phiếu mượn M.</t>
-        </is>
-      </c>
-      <c r="H197" s="15" t="inlineStr">
-        <is>
-          <t>Lý do từ chối: Không đủ chứng từ</t>
-        </is>
-      </c>
-      <c r="I197" s="15" t="inlineStr">
-        <is>
-          <t>- Hạn trả của M giữ nguyên như trước khi lập phiếu gia hạn.</t>
         </is>
       </c>
       <c r="J197" s="15" t="inlineStr"/>
@@ -12864,13 +12880,289 @@
       <c r="P197" s="16" t="inlineStr"/>
       <c r="Q197" s="16" t="inlineStr"/>
     </row>
+    <row r="198" ht="53" customHeight="1">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
+        </is>
+      </c>
+      <c r="C198" s="16" t="inlineStr">
+        <is>
+          <t>TC_12.003</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>Từ chối rồi lập phiếu mới</t>
+        </is>
+      </c>
+      <c r="E198" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F198" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu gia hạn X của M bị TP từ chối.</t>
+        </is>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>1. Người lập mở X tìm cách gửi lại.
+2. Vào Tạo mới, chọn lại M, gửi phiếu mới.
+3. TP và KT duyệt phiếu mới.</t>
+        </is>
+      </c>
+      <c r="H198" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I198" s="15" t="inlineStr">
+        <is>
+          <t>- X không có nút gửi lại / sửa, giữ Không duyệt.
+- M có trong popup chọn phiếu ngay sau khi X bị từ chối.
+- Phiếu mới đi hết luồng, M đổi hạn; X vẫn Không duyệt.</t>
+        </is>
+      </c>
+      <c r="J198" s="15" t="inlineStr"/>
+      <c r="K198" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L198" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M198" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N198" s="15" t="inlineStr"/>
+      <c r="O198" s="16" t="inlineStr"/>
+      <c r="P198" s="16" t="inlineStr"/>
+      <c r="Q198" s="16" t="inlineStr"/>
+    </row>
+    <row r="199" ht="46" customHeight="1">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>TC_12.004</t>
+        </is>
+      </c>
+      <c r="D199" s="15" t="inlineStr">
+        <is>
+          <t>Gia hạn hai lần liên tiếp cùng phiếu mượn</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F199" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu mượn M hạn 23/09. Số ngày mượn tối đa 7.</t>
+        </is>
+      </c>
+      <c r="G199" s="15" t="inlineStr">
+        <is>
+          <t>1. Lập và duyệt xong phiếu gia hạn M sang 03/10.
+2. Lập tiếp phiếu gia hạn M.</t>
+        </is>
+      </c>
+      <c r="H199" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I199" s="15" t="inlineStr">
+        <is>
+          <t>- Lần 2, Ngày hẹn trả hiện 03/10/2026; lịch chỉ cho chọn từ 04/10 đến ngày trần.
+- Không lập được phiếu có ngày mới trùng hoặc trước 03/10.</t>
+        </is>
+      </c>
+      <c r="J199" s="15" t="inlineStr"/>
+      <c r="K199" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L199" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M199" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N199" s="15" t="inlineStr"/>
+      <c r="O199" s="16" t="inlineStr"/>
+      <c r="P199" s="16" t="inlineStr"/>
+      <c r="Q199" s="16" t="inlineStr"/>
+    </row>
+    <row r="200" ht="34" customHeight="1">
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>TC_12.005</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>Kiểm tra chéo với màn Hàng sắp hết hạn mượn / Danh sách hàng mượn</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F200" s="15" t="inlineStr">
+        <is>
+          <t>Vừa duyệt xong phiếu gia hạn M sang 05/10/2026.</t>
+        </is>
+      </c>
+      <c r="G200" s="15" t="inlineStr">
+        <is>
+          <t>1. Mở Tài chính &gt; Mượn hàng &gt; Danh sách hàng mượn, tìm hàng của M.
+2. Mở Hàng sắp hết hạn mượn.</t>
+        </is>
+      </c>
+      <c r="H200" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I200" s="15" t="inlineStr">
+        <is>
+          <t>- Hạn trả của hàng thuộc M hiện 05/10/2026.
+- M không còn nằm trong diện sắp hết hạn theo hạn cũ.</t>
+        </is>
+      </c>
+      <c r="J200" s="15" t="inlineStr"/>
+      <c r="K200" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L200" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M200" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N200" s="15" t="inlineStr"/>
+      <c r="O200" s="16" t="inlineStr"/>
+      <c r="P200" s="16" t="inlineStr"/>
+      <c r="Q200" s="16" t="inlineStr"/>
+    </row>
+    <row r="201" ht="34" customHeight="1">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>YC gia hạn hàng mượn</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>LUỒNG NGHIỆP VỤ ĐẦU CUỐI</t>
+        </is>
+      </c>
+      <c r="C201" s="16" t="inlineStr">
+        <is>
+          <t>TC_12.006</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="inlineStr">
+        <is>
+          <t>Từ chối không đụng phiếu mượn</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F201" s="15" t="inlineStr">
+        <is>
+          <t>Phiếu gia hạn M đã qua TP, đang Chờ KT duyệt.</t>
+        </is>
+      </c>
+      <c r="G201" s="15" t="inlineStr">
+        <is>
+          <t>1. Kế toán từ chối.
+2. Mở phiếu mượn M.</t>
+        </is>
+      </c>
+      <c r="H201" s="15" t="inlineStr">
+        <is>
+          <t>Lý do từ chối: Không đủ chứng từ</t>
+        </is>
+      </c>
+      <c r="I201" s="15" t="inlineStr">
+        <is>
+          <t>- Hạn trả của M giữ nguyên như trước khi lập phiếu gia hạn.</t>
+        </is>
+      </c>
+      <c r="J201" s="15" t="inlineStr"/>
+      <c r="K201" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="L201" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M201" s="16" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N201" s="15" t="inlineStr"/>
+      <c r="O201" s="16" t="inlineStr"/>
+      <c r="P201" s="16" t="inlineStr"/>
+      <c r="Q201" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="C113:Q113"/>
     <mergeCell ref="C65:Q65"/>
     <mergeCell ref="B9:N9"/>
-    <mergeCell ref="C143:Q143"/>
     <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C183:Q183"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="I11:J11"/>
@@ -12891,32 +13183,33 @@
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="C32:Q32"/>
     <mergeCell ref="M12:N12"/>
+    <mergeCell ref="C174:Q174"/>
+    <mergeCell ref="C161:Q161"/>
     <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="C170:Q170"/>
+    <mergeCell ref="C140:Q140"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="C18:Q18"/>
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="C101:Q101"/>
-    <mergeCell ref="C136:Q136"/>
-    <mergeCell ref="C179:Q179"/>
     <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="C157:Q157"/>
+    <mergeCell ref="C195:Q195"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="C191:Q191"/>
+    <mergeCell ref="C104:Q104"/>
+    <mergeCell ref="C116:Q116"/>
     <mergeCell ref="C45:Q45"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="C79:Q79"/>
     <mergeCell ref="F11:H15"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="B10:N10"/>
+    <mergeCell ref="C147:Q147"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="K18:M247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K18:M251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
-    <dataValidation sqref="O18:Q247" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O18:Q251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P,F,PE"</formula1>
     </dataValidation>
   </dataValidations>
